--- a/listas_precios/CGA.xlsx
+++ b/listas_precios/CGA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\APP PARABRISAS\listas_precios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2CB6921-EBCE-4D5D-B88B-6A33CD89D3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369DD23E-652F-4220-AE1C-9439D7F45187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4C7B1A3A-BCB1-4369-A528-0A366639E170}"/>
   </bookViews>
@@ -4729,7 +4729,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
@@ -4744,15 +4744,17 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5072,7 +5074,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="56.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5080,24 +5082,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="C2" s="2"/>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="C3" s="6"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+      <c r="C4" s="6"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -5106,18 +5108,18 @@
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="6"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -5126,7 +5128,7 @@
       <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <v>181571.35700000002</v>
       </c>
     </row>
@@ -5137,7 +5139,7 @@
       <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>168855.53300000002</v>
       </c>
     </row>
@@ -5148,7 +5150,7 @@
       <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <v>100024.08900000001</v>
       </c>
     </row>
@@ -5159,7 +5161,7 @@
       <c r="B10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>92837.272000000012</v>
       </c>
     </row>
@@ -5170,7 +5172,7 @@
       <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <v>118447.47200000001</v>
       </c>
     </row>
@@ -5181,7 +5183,7 @@
       <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <v>110164.49400000001</v>
       </c>
     </row>
@@ -5192,7 +5194,7 @@
       <c r="B13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="8">
         <v>123876.10400000001</v>
       </c>
     </row>
@@ -5203,7 +5205,7 @@
       <c r="B14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="8">
         <v>115220.19190000001</v>
       </c>
     </row>
@@ -5214,7 +5216,7 @@
       <c r="B15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <v>121708.136</v>
       </c>
     </row>
@@ -5225,7 +5227,7 @@
       <c r="B16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <v>113185.3404</v>
       </c>
     </row>
@@ -5236,7 +5238,7 @@
       <c r="B17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <v>110015.16900000001</v>
       </c>
     </row>
@@ -5247,7 +5249,7 @@
       <c r="B18" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <v>105947.08300000001</v>
       </c>
     </row>
@@ -5258,7 +5260,7 @@
       <c r="B19" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>114549.82</v>
       </c>
     </row>
@@ -5269,7 +5271,7 @@
       <c r="B20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>109297.62800000001</v>
       </c>
     </row>
@@ -5280,7 +5282,7 @@
       <c r="B21" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <v>135401.93700000001</v>
       </c>
     </row>
@@ -5291,7 +5293,7 @@
       <c r="B22" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="8">
         <v>125937.66900000001</v>
       </c>
     </row>
@@ -5302,7 +5304,7 @@
       <c r="B23" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <v>104509.43800000001</v>
       </c>
     </row>
@@ -5313,7 +5315,7 @@
       <c r="B24" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="8">
         <v>102083.432</v>
       </c>
     </row>
@@ -5324,7 +5326,7 @@
       <c r="B25" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="8">
         <v>185768.29699999999</v>
       </c>
     </row>
@@ -5335,7 +5337,7 @@
       <c r="B26" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="8">
         <v>152831.008</v>
       </c>
     </row>
@@ -5346,7 +5348,7 @@
       <c r="B27" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="8">
         <v>301650.14000000007</v>
       </c>
     </row>
@@ -5357,7 +5359,7 @@
       <c r="B28" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="8">
         <v>280004.49400000001</v>
       </c>
     </row>
@@ -5368,7 +5370,7 @@
       <c r="B29" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="8">
         <v>123511.0778</v>
       </c>
     </row>
@@ -5379,7 +5381,7 @@
       <c r="B30" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="8">
         <v>118152.57630000002</v>
       </c>
     </row>
@@ -5390,7 +5392,7 @@
       <c r="B31" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="8">
         <v>171786.83500000002</v>
       </c>
     </row>
@@ -5401,7 +5403,7 @@
       <c r="B32" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="8">
         <v>163876.63600000003</v>
       </c>
     </row>
@@ -5412,7 +5414,7 @@
       <c r="B33" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="8">
         <v>86254.894</v>
       </c>
     </row>
@@ -5423,7 +5425,7 @@
       <c r="B34" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="8">
         <v>167794.14300000001</v>
       </c>
     </row>
@@ -5434,7 +5436,7 @@
       <c r="B35" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="8">
         <v>150300.42500000002</v>
       </c>
     </row>
@@ -5445,7 +5447,7 @@
       <c r="B36" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="8">
         <v>193485.13800000001</v>
       </c>
     </row>
@@ -5456,7 +5458,7 @@
       <c r="B37" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="8">
         <v>178097.72200000001</v>
       </c>
     </row>
@@ -5467,7 +5469,7 @@
       <c r="B38" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="8">
         <v>183672.90700000001</v>
       </c>
     </row>
@@ -5478,7 +5480,7 @@
       <c r="B39" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="8">
         <v>122545.30200000001</v>
       </c>
     </row>
@@ -5489,7 +5491,7 @@
       <c r="B40" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="8">
         <v>113976.88500000001</v>
       </c>
     </row>
@@ -5500,7 +5502,7 @@
       <c r="B41" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="8">
         <v>171786.81740000003</v>
       </c>
     </row>
@@ -5511,7 +5513,7 @@
       <c r="B42" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="8">
         <v>163876.63159999999</v>
       </c>
     </row>
@@ -5522,7 +5524,7 @@
       <c r="B43" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="8">
         <v>198016.69470000002</v>
       </c>
     </row>
@@ -5533,7 +5535,7 @@
       <c r="B44" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="8">
         <v>184156.61000000002</v>
       </c>
     </row>
@@ -5544,7 +5546,7 @@
       <c r="B45" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="8">
         <v>171786.82400000002</v>
       </c>
     </row>
@@ -5555,7 +5557,7 @@
       <c r="B46" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="8">
         <v>163876.63600000003</v>
       </c>
     </row>
@@ -5566,7 +5568,7 @@
       <c r="B47" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="8">
         <v>129766.37300000001</v>
       </c>
     </row>
@@ -5577,7 +5579,7 @@
       <c r="B48" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C48" s="7">
+      <c r="C48" s="8">
         <v>120679.04200000002</v>
       </c>
     </row>
@@ -5588,7 +5590,7 @@
       <c r="B49" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C49" s="8">
         <v>198203.54400000002</v>
       </c>
     </row>
@@ -5599,7 +5601,7 @@
       <c r="B50" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C50" s="7">
+      <c r="C50" s="8">
         <v>173864.15200000003</v>
       </c>
     </row>
@@ -5610,7 +5612,7 @@
       <c r="B51" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C51" s="8">
         <v>285330.848</v>
       </c>
     </row>
@@ -5621,18 +5623,18 @@
       <c r="B52" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C52" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C53" s="7"/>
+      <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
@@ -5641,7 +5643,7 @@
       <c r="B54" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C54" s="8">
         <v>161746.65100000001</v>
       </c>
     </row>
@@ -5652,7 +5654,7 @@
       <c r="B55" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C55" s="7">
+      <c r="C55" s="8">
         <v>150447.07700000002</v>
       </c>
     </row>
@@ -5663,7 +5665,7 @@
       <c r="B56" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="8">
         <v>236635.94900000002</v>
       </c>
     </row>
@@ -5674,18 +5676,18 @@
       <c r="B57" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C57" s="7">
+      <c r="C57" s="8">
         <v>220065.10900000003</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C58" s="7"/>
+      <c r="C58" s="8"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
@@ -5694,7 +5696,7 @@
       <c r="B59" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C59" s="7">
+      <c r="C59" s="8">
         <v>110677.20180000001</v>
       </c>
     </row>
@@ -5705,7 +5707,7 @@
       <c r="B60" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C60" s="8">
         <v>120885.25900000001</v>
       </c>
     </row>
@@ -5716,7 +5718,7 @@
       <c r="B61" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C61" s="8">
         <v>104532.505</v>
       </c>
     </row>
@@ -5727,7 +5729,7 @@
       <c r="B62" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C62" s="8">
         <v>109482.4379</v>
       </c>
     </row>
@@ -5738,7 +5740,7 @@
       <c r="B63" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C63" s="7">
+      <c r="C63" s="8">
         <v>200800.64400000003</v>
       </c>
     </row>
@@ -5749,7 +5751,7 @@
       <c r="B64" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C64" s="7">
+      <c r="C64" s="8">
         <v>186757.39500000002</v>
       </c>
     </row>
@@ -5760,7 +5762,7 @@
       <c r="B65" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C65" s="7">
+      <c r="C65" s="8">
         <v>183206.606</v>
       </c>
     </row>
@@ -5771,7 +5773,7 @@
       <c r="B66" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C66" s="7">
+      <c r="C66" s="8">
         <v>178318.76700000002</v>
       </c>
     </row>
@@ -5782,7 +5784,7 @@
       <c r="B67" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C67" s="7">
+      <c r="C67" s="8">
         <v>198454.10200000001</v>
       </c>
     </row>
@@ -5793,7 +5795,7 @@
       <c r="B68" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C68" s="7">
+      <c r="C68" s="8">
         <v>184213.30400000003</v>
       </c>
     </row>
@@ -5804,7 +5806,7 @@
       <c r="B69" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C69" s="7">
+      <c r="C69" s="8">
         <v>278846.11920000002</v>
       </c>
     </row>
@@ -5815,7 +5817,7 @@
       <c r="B70" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C70" s="7">
+      <c r="C70" s="8">
         <v>256126.73020000002</v>
       </c>
     </row>
@@ -5826,7 +5828,7 @@
       <c r="B71" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C71" s="7">
+      <c r="C71" s="8">
         <v>162842.50400000002</v>
       </c>
     </row>
@@ -5837,7 +5839,7 @@
       <c r="B72" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C72" s="7">
+      <c r="C72" s="8">
         <v>151164.75</v>
       </c>
     </row>
@@ -5848,7 +5850,7 @@
       <c r="B73" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C73" s="7">
+      <c r="C73" s="8">
         <v>129610.62400000001</v>
       </c>
     </row>
@@ -5859,7 +5861,7 @@
       <c r="B74" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C74" s="7">
+      <c r="C74" s="8">
         <v>120885.25900000001</v>
       </c>
     </row>
@@ -5870,7 +5872,7 @@
       <c r="B75" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C75" s="7">
+      <c r="C75" s="8">
         <v>130499.974</v>
       </c>
     </row>
@@ -5881,7 +5883,7 @@
       <c r="B76" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C76" s="7">
+      <c r="C76" s="8">
         <v>121369.90800000001</v>
       </c>
     </row>
@@ -5892,7 +5894,7 @@
       <c r="B77" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C77" s="7">
+      <c r="C77" s="8">
         <v>152997.10800000001</v>
       </c>
     </row>
@@ -5903,7 +5905,7 @@
       <c r="B78" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C78" s="7">
+      <c r="C78" s="8">
         <v>163708.80900000001</v>
       </c>
     </row>
@@ -5914,7 +5916,7 @@
       <c r="B79" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C79" s="7">
+      <c r="C79" s="8">
         <v>142298.15600000002</v>
       </c>
     </row>
@@ -5925,7 +5927,7 @@
       <c r="B80" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C80" s="7">
+      <c r="C80" s="8">
         <v>152256.94</v>
       </c>
     </row>
@@ -5936,7 +5938,7 @@
       <c r="B81" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C81" s="7">
+      <c r="C81" s="8">
         <v>101218.70000000001</v>
       </c>
     </row>
@@ -5947,7 +5949,7 @@
       <c r="B82" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C82" s="7">
+      <c r="C82" s="8">
         <v>93116.122000000018</v>
       </c>
     </row>
@@ -5958,7 +5960,7 @@
       <c r="B83" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C83" s="7">
+      <c r="C83" s="8">
         <v>130499.96300000002</v>
       </c>
     </row>
@@ -5969,7 +5971,7 @@
       <c r="B84" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C84" s="7">
+      <c r="C84" s="8">
         <v>121369.93000000001</v>
       </c>
     </row>
@@ -5980,7 +5982,7 @@
       <c r="B85" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C85" s="7">
+      <c r="C85" s="8">
         <v>444136.07700000005</v>
       </c>
     </row>
@@ -5991,7 +5993,7 @@
       <c r="B86" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C86" s="7">
+      <c r="C86" s="8">
         <v>145440.29500000001</v>
       </c>
     </row>
@@ -6002,18 +6004,18 @@
       <c r="B87" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C87" s="7">
+      <c r="C87" s="8">
         <v>132218.44899999999</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B88" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C88" s="7"/>
+      <c r="C88" s="8"/>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
@@ -6022,7 +6024,7 @@
       <c r="B89" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C89" s="7">
+      <c r="C89" s="8">
         <v>179885.86000000002</v>
       </c>
     </row>
@@ -6033,18 +6035,18 @@
       <c r="B90" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C90" s="7">
+      <c r="C90" s="8">
         <v>167293.40100000001</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C91" s="7"/>
+      <c r="C91" s="8"/>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
@@ -6053,7 +6055,7 @@
       <c r="B92" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C92" s="7">
+      <c r="C92" s="8">
         <v>135401.93700000001</v>
       </c>
     </row>
@@ -6064,7 +6066,7 @@
       <c r="B93" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C93" s="7">
+      <c r="C93" s="8">
         <v>125937.66900000001</v>
       </c>
     </row>
@@ -6075,7 +6077,7 @@
       <c r="B94" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C94" s="7">
+      <c r="C94" s="8">
         <v>104630.933</v>
       </c>
     </row>
@@ -6086,7 +6088,7 @@
       <c r="B95" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C95" s="7">
+      <c r="C95" s="8">
         <v>93631.23000000001</v>
       </c>
     </row>
@@ -6097,7 +6099,7 @@
       <c r="B96" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C96" s="7">
+      <c r="C96" s="8">
         <v>117245.66700000002</v>
       </c>
     </row>
@@ -6108,7 +6110,7 @@
       <c r="B97" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C97" s="7">
+      <c r="C97" s="8">
         <v>108836.398</v>
       </c>
     </row>
@@ -6119,7 +6121,7 @@
       <c r="B98" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C98" s="7">
+      <c r="C98" s="8">
         <v>137522.79200000002</v>
       </c>
     </row>
@@ -6130,7 +6132,7 @@
       <c r="B99" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C99" s="7">
+      <c r="C99" s="8">
         <v>127892.45700000001</v>
       </c>
     </row>
@@ -6141,7 +6143,7 @@
       <c r="B100" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C100" s="7">
+      <c r="C100" s="8">
         <v>122827.12200000002</v>
       </c>
     </row>
@@ -6152,7 +6154,7 @@
       <c r="B101" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C101" s="7">
+      <c r="C101" s="8">
         <v>109968.265</v>
       </c>
     </row>
@@ -6163,7 +6165,7 @@
       <c r="B102" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C102" s="7">
+      <c r="C102" s="8">
         <v>153388.73000000001</v>
       </c>
     </row>
@@ -6174,7 +6176,7 @@
       <c r="B103" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C103" s="7">
+      <c r="C103" s="8">
         <v>142656.459</v>
       </c>
     </row>
@@ -6185,7 +6187,7 @@
       <c r="B104" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C104" s="7">
+      <c r="C104" s="8">
         <v>168281.432</v>
       </c>
     </row>
@@ -6196,7 +6198,7 @@
       <c r="B105" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C105" s="7">
+      <c r="C105" s="8">
         <v>150409.50100000002</v>
       </c>
     </row>
@@ -6207,7 +6209,7 @@
       <c r="B106" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C106" s="7">
+      <c r="C106" s="8">
         <v>158188.80000000002</v>
       </c>
     </row>
@@ -6218,7 +6220,7 @@
       <c r="B107" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C107" s="7">
+      <c r="C107" s="8">
         <v>149664.90000000002</v>
       </c>
     </row>
@@ -6229,7 +6231,7 @@
       <c r="B108" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C108" s="7">
+      <c r="C108" s="8">
         <v>216681.83900000001</v>
       </c>
     </row>
@@ -6240,18 +6242,18 @@
       <c r="B109" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C109" s="7">
+      <c r="C109" s="8">
         <v>196983.47900000002</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B110" s="6" t="s">
+      <c r="B110" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C110" s="7"/>
+      <c r="C110" s="8"/>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
@@ -6260,7 +6262,7 @@
       <c r="B111" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C111" s="7">
+      <c r="C111" s="8">
         <v>121643.33500000002</v>
       </c>
     </row>
@@ -6271,7 +6273,7 @@
       <c r="B112" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C112" s="7">
+      <c r="C112" s="8">
         <v>130159.348</v>
       </c>
     </row>
@@ -6282,7 +6284,7 @@
       <c r="B113" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C113" s="7">
+      <c r="C113" s="8">
         <v>113125.63900000001</v>
       </c>
     </row>
@@ -6293,7 +6295,7 @@
       <c r="B114" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C114" s="7">
+      <c r="C114" s="8">
         <v>121046.33200000001</v>
       </c>
     </row>
@@ -6304,7 +6306,7 @@
       <c r="B115" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C115" s="7">
+      <c r="C115" s="8">
         <v>295474.26699999999</v>
       </c>
     </row>
@@ -6315,7 +6317,7 @@
       <c r="B116" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C116" s="7">
+      <c r="C116" s="8">
         <v>274785.85200000001</v>
       </c>
     </row>
@@ -6326,7 +6328,7 @@
       <c r="B117" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="C117" s="7">
+      <c r="C117" s="8">
         <v>156597.00100000002</v>
       </c>
     </row>
@@ -6337,7 +6339,7 @@
       <c r="B118" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="C118" s="7">
+      <c r="C118" s="8">
         <v>145637.62400000001</v>
       </c>
     </row>
@@ -6348,7 +6350,7 @@
       <c r="B119" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C119" s="7">
+      <c r="C119" s="8">
         <v>129838.67600000002</v>
       </c>
     </row>
@@ -6359,7 +6361,7 @@
       <c r="B120" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C120" s="7">
+      <c r="C120" s="8">
         <v>118057.09300000001</v>
       </c>
     </row>
@@ -6370,7 +6372,7 @@
       <c r="B121" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="C121" s="7">
+      <c r="C121" s="8">
         <v>153200.86540000001</v>
       </c>
     </row>
@@ -6381,7 +6383,7 @@
       <c r="B122" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C122" s="7">
+      <c r="C122" s="8">
         <v>142483.429</v>
       </c>
     </row>
@@ -6392,7 +6394,7 @@
       <c r="B123" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C123" s="7">
+      <c r="C123" s="8">
         <v>614375.92700000003</v>
       </c>
     </row>
@@ -6403,7 +6405,7 @@
       <c r="B124" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C124" s="7">
+      <c r="C124" s="8">
         <v>558504.17700000003</v>
       </c>
     </row>
@@ -6414,7 +6416,7 @@
       <c r="B125" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="C125" s="7">
+      <c r="C125" s="8">
         <v>121708.97200000001</v>
       </c>
     </row>
@@ -6425,7 +6427,7 @@
       <c r="B126" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C126" s="7">
+      <c r="C126" s="8">
         <v>113189.758</v>
       </c>
     </row>
@@ -6436,7 +6438,7 @@
       <c r="B127" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C127" s="7">
+      <c r="C127" s="8">
         <v>141676.766</v>
       </c>
     </row>
@@ -6447,7 +6449,7 @@
       <c r="B128" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C128" s="7">
+      <c r="C128" s="8">
         <v>131352.1</v>
       </c>
     </row>
@@ -6458,7 +6460,7 @@
       <c r="B129" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C129" s="7">
+      <c r="C129" s="8">
         <v>122154.12000000001</v>
       </c>
     </row>
@@ -6469,7 +6471,7 @@
       <c r="B130" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C130" s="7">
+      <c r="C130" s="8">
         <v>113702.12700000002</v>
       </c>
     </row>
@@ -6480,7 +6482,7 @@
       <c r="B131" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C131" s="7">
+      <c r="C131" s="8">
         <v>150000.00400000002</v>
       </c>
     </row>
@@ -6491,7 +6493,7 @@
       <c r="B132" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C132" s="7">
+      <c r="C132" s="8">
         <v>431916.12200000003</v>
       </c>
     </row>
@@ -6502,7 +6504,7 @@
       <c r="B133" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C133" s="7">
+      <c r="C133" s="8">
         <v>372347.701</v>
       </c>
     </row>
@@ -6513,7 +6515,7 @@
       <c r="B134" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C134" s="7">
+      <c r="C134" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6524,7 +6526,7 @@
       <c r="B135" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="C135" s="7">
+      <c r="C135" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6535,7 +6537,7 @@
       <c r="B136" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C136" s="7">
+      <c r="C136" s="8">
         <v>121049.819</v>
       </c>
     </row>
@@ -6546,7 +6548,7 @@
       <c r="B137" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="C137" s="7">
+      <c r="C137" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6557,7 +6559,7 @@
       <c r="B138" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C138" s="7">
+      <c r="C138" s="8">
         <v>112573.175</v>
       </c>
     </row>
@@ -6568,7 +6570,7 @@
       <c r="B139" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C139" s="7">
+      <c r="C139" s="8">
         <v>110120.32900000001</v>
       </c>
     </row>
@@ -6579,7 +6581,7 @@
       <c r="B140" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="C140" s="7">
+      <c r="C140" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6590,7 +6592,7 @@
       <c r="B141" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C141" s="7">
+      <c r="C141" s="8">
         <v>102409.61500000001</v>
       </c>
     </row>
@@ -6601,7 +6603,7 @@
       <c r="B142" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="C142" s="7">
+      <c r="C142" s="8">
         <v>159078.02900000004</v>
       </c>
     </row>
@@ -6612,7 +6614,7 @@
       <c r="B143" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="C143" s="7">
+      <c r="C143" s="8">
         <v>144616.39500000002</v>
       </c>
     </row>
@@ -6623,7 +6625,7 @@
       <c r="B144" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="C144" s="7">
+      <c r="C144" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6634,7 +6636,7 @@
       <c r="B145" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C145" s="7">
+      <c r="C145" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6645,7 +6647,7 @@
       <c r="B146" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="C146" s="7">
+      <c r="C146" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6656,7 +6658,7 @@
       <c r="B147" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C147" s="7">
+      <c r="C147" s="8">
         <v>127313.78000000001</v>
       </c>
     </row>
@@ -6667,7 +6669,7 @@
       <c r="B148" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C148" s="7">
+      <c r="C148" s="8">
         <v>130159.35900000001</v>
       </c>
     </row>
@@ -6678,7 +6680,7 @@
       <c r="B149" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C149" s="7">
+      <c r="C149" s="8">
         <v>117727.11500000001</v>
       </c>
     </row>
@@ -6689,7 +6691,7 @@
       <c r="B150" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="C150" s="7">
+      <c r="C150" s="8">
         <v>121046.33200000001</v>
       </c>
     </row>
@@ -6700,7 +6702,7 @@
       <c r="B151" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="C151" s="7">
+      <c r="C151" s="8">
         <v>159424.1</v>
       </c>
     </row>
@@ -6711,18 +6713,18 @@
       <c r="B152" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="C152" s="7">
+      <c r="C152" s="8">
         <v>150873.81100000002</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="6" t="s">
+      <c r="A153" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="B153" s="6" t="s">
+      <c r="B153" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="C153" s="7"/>
+      <c r="C153" s="8"/>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
@@ -6731,7 +6733,7 @@
       <c r="B154" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C154" s="7">
+      <c r="C154" s="8">
         <v>205241.14600000001</v>
       </c>
     </row>
@@ -6742,7 +6744,7 @@
       <c r="B155" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C155" s="7">
+      <c r="C155" s="8">
         <v>196891.80499999999</v>
       </c>
     </row>
@@ -6753,7 +6755,7 @@
       <c r="B156" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="C156" s="7">
+      <c r="C156" s="8">
         <v>218615.54</v>
       </c>
     </row>
@@ -6764,7 +6766,7 @@
       <c r="B157" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C157" s="7">
+      <c r="C157" s="8">
         <v>203117.772</v>
       </c>
     </row>
@@ -6775,7 +6777,7 @@
       <c r="B158" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C158" s="7">
+      <c r="C158" s="8">
         <v>141690.02100000001</v>
       </c>
     </row>
@@ -6786,7 +6788,7 @@
       <c r="B159" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C159" s="7">
+      <c r="C159" s="8">
         <v>116260.03400000001</v>
       </c>
     </row>
@@ -6797,7 +6799,7 @@
       <c r="B160" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="C160" s="7">
+      <c r="C160" s="8">
         <v>225010.72000000003</v>
       </c>
     </row>
@@ -6808,7 +6810,7 @@
       <c r="B161" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="C161" s="7">
+      <c r="C161" s="8">
         <v>220807.774</v>
       </c>
     </row>
@@ -6819,7 +6821,7 @@
       <c r="B162" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C162" s="7">
+      <c r="C162" s="8">
         <v>167082.78400000001</v>
       </c>
     </row>
@@ -6830,7 +6832,7 @@
       <c r="B163" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="C163" s="7">
+      <c r="C163" s="8">
         <v>155382.84300000002</v>
       </c>
     </row>
@@ -6841,7 +6843,7 @@
       <c r="B164" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C164" s="7">
+      <c r="C164" s="8">
         <v>224227.85</v>
       </c>
     </row>
@@ -6852,7 +6854,7 @@
       <c r="B165" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C165" s="7">
+      <c r="C165" s="8">
         <v>217778.62700000004</v>
       </c>
     </row>
@@ -6863,7 +6865,7 @@
       <c r="B166" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="C166" s="7">
+      <c r="C166" s="8">
         <v>148414.80499999999</v>
       </c>
     </row>
@@ -6874,7 +6876,7 @@
       <c r="B167" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C167" s="7">
+      <c r="C167" s="8">
         <v>139502.81400000001</v>
       </c>
     </row>
@@ -6885,7 +6887,7 @@
       <c r="B168" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="C168" s="7">
+      <c r="C168" s="8">
         <v>444142.60000000003</v>
       </c>
     </row>
@@ -6896,7 +6898,7 @@
       <c r="B169" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="C169" s="7">
+      <c r="C169" s="8">
         <v>143855.42600000001</v>
       </c>
     </row>
@@ -6907,7 +6909,7 @@
       <c r="B170" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C170" s="7">
+      <c r="C170" s="8">
         <v>133409.1</v>
       </c>
     </row>
@@ -6918,7 +6920,7 @@
       <c r="B171" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C171" s="7">
+      <c r="C171" s="8">
         <v>156972.97000000003</v>
       </c>
     </row>
@@ -6929,7 +6931,7 @@
       <c r="B172" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="C172" s="7">
+      <c r="C172" s="8">
         <v>148623.43100000001</v>
       </c>
     </row>
@@ -6940,7 +6942,7 @@
       <c r="B173" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="C173" s="7">
+      <c r="C173" s="8">
         <v>191649.15000000002</v>
       </c>
     </row>
@@ -6951,7 +6953,7 @@
       <c r="B174" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C174" s="7">
+      <c r="C174" s="8">
         <v>176317.21800000002</v>
       </c>
     </row>
@@ -6962,7 +6964,7 @@
       <c r="B175" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="C175" s="7">
+      <c r="C175" s="8">
         <v>163864.008</v>
       </c>
     </row>
@@ -6973,7 +6975,7 @@
       <c r="B176" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="C176" s="7">
+      <c r="C176" s="8">
         <v>148967.28</v>
       </c>
     </row>
@@ -6984,7 +6986,7 @@
       <c r="B177" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="C177" s="7">
+      <c r="C177" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6995,18 +6997,18 @@
       <c r="B178" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="C178" s="7">
+      <c r="C178" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="6" t="s">
+      <c r="A179" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="B179" s="6" t="s">
+      <c r="B179" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="C179" s="7"/>
+      <c r="C179" s="8"/>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
@@ -7015,7 +7017,7 @@
       <c r="B180" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="C180" s="7">
+      <c r="C180" s="8">
         <v>151261.32999999999</v>
       </c>
     </row>
@@ -7026,7 +7028,7 @@
       <c r="B181" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="C181" s="7">
+      <c r="C181" s="8">
         <v>140998.63800000001</v>
       </c>
     </row>
@@ -7037,7 +7039,7 @@
       <c r="B182" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="C182" s="7">
+      <c r="C182" s="8">
         <v>222924.889</v>
       </c>
     </row>
@@ -7048,7 +7050,7 @@
       <c r="B183" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="C183" s="7">
+      <c r="C183" s="8">
         <v>206923.38700000002</v>
       </c>
     </row>
@@ -7059,7 +7061,7 @@
       <c r="B184" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="C184" s="7">
+      <c r="C184" s="8">
         <v>294271.21020000003</v>
       </c>
     </row>
@@ -7070,7 +7072,7 @@
       <c r="B185" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="C185" s="7">
+      <c r="C185" s="8">
         <v>273674.86300000001</v>
       </c>
     </row>
@@ -7081,7 +7083,7 @@
       <c r="B186" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="C186" s="7">
+      <c r="C186" s="8">
         <v>147113.81849999999</v>
       </c>
     </row>
@@ -7092,7 +7094,7 @@
       <c r="B187" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="C187" s="7">
+      <c r="C187" s="8">
         <v>136558.90600000002</v>
       </c>
     </row>
@@ -7103,7 +7105,7 @@
       <c r="B188" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="C188" s="7">
+      <c r="C188" s="8">
         <v>182509.64380000002</v>
       </c>
     </row>
@@ -7114,7 +7116,7 @@
       <c r="B189" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="C189" s="7">
+      <c r="C189" s="8">
         <v>177809.15900000001</v>
       </c>
     </row>
@@ -7125,7 +7127,7 @@
       <c r="B190" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="C190" s="7">
+      <c r="C190" s="8">
         <v>169415.21299999999</v>
       </c>
     </row>
@@ -7136,7 +7138,7 @@
       <c r="B191" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="C191" s="7">
+      <c r="C191" s="8">
         <v>175142.74030000003</v>
       </c>
     </row>
@@ -7147,7 +7149,7 @@
       <c r="B192" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="C192" s="7">
+      <c r="C192" s="8">
         <v>155826.01100000003</v>
       </c>
     </row>
@@ -7158,7 +7160,7 @@
       <c r="B193" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="C193" s="7">
+      <c r="C193" s="8">
         <v>158119.87400000001</v>
       </c>
     </row>
@@ -7169,7 +7171,7 @@
       <c r="B194" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="C194" s="7">
+      <c r="C194" s="8">
         <v>252884.20300000004</v>
       </c>
     </row>
@@ -7180,7 +7182,7 @@
       <c r="B195" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="C195" s="7">
+      <c r="C195" s="8">
         <v>232653.46500000003</v>
       </c>
     </row>
@@ -7191,7 +7193,7 @@
       <c r="B196" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="C196" s="7">
+      <c r="C196" s="8">
         <v>129373.92600000002</v>
       </c>
     </row>
@@ -7202,7 +7204,7 @@
       <c r="B197" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="C197" s="7">
+      <c r="C197" s="8">
         <v>121257.66400000002</v>
       </c>
     </row>
@@ -7213,7 +7215,7 @@
       <c r="B198" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="C198" s="7">
+      <c r="C198" s="8">
         <v>263363.74900000001</v>
       </c>
     </row>
@@ -7224,18 +7226,18 @@
       <c r="B199" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="C199" s="7">
+      <c r="C199" s="8">
         <v>258993.09700000001</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="6" t="s">
+      <c r="A200" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="B200" s="6" t="s">
+      <c r="B200" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="C200" s="7"/>
+      <c r="C200" s="8"/>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
@@ -7244,7 +7246,7 @@
       <c r="B201" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="C201" s="7">
+      <c r="C201" s="8">
         <v>170020.46600000001</v>
       </c>
     </row>
@@ -7255,7 +7257,7 @@
       <c r="B202" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="C202" s="7">
+      <c r="C202" s="8">
         <v>158138.60700000002</v>
       </c>
     </row>
@@ -7266,7 +7268,7 @@
       <c r="B203" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="C203" s="7">
+      <c r="C203" s="8">
         <v>308707.37700000004</v>
       </c>
     </row>
@@ -7277,7 +7279,7 @@
       <c r="B204" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="C204" s="7">
+      <c r="C204" s="8">
         <v>297752.45500000002</v>
       </c>
     </row>
@@ -7288,18 +7290,18 @@
       <c r="B205" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="C205" s="7">
+      <c r="C205" s="8">
         <v>174675.30300000001</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="6" t="s">
+      <c r="A206" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="B206" s="6" t="s">
+      <c r="B206" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="C206" s="7"/>
+      <c r="C206" s="8"/>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
@@ -7308,7 +7310,7 @@
       <c r="B207" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="C207" s="7">
+      <c r="C207" s="8">
         <v>507725.83400000003</v>
       </c>
     </row>
@@ -7319,7 +7321,7 @@
       <c r="B208" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="C208" s="7">
+      <c r="C208" s="8">
         <v>461576.45600000006</v>
       </c>
     </row>
@@ -7330,7 +7332,7 @@
       <c r="B209" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="C209" s="7">
+      <c r="C209" s="8">
         <v>332340.723</v>
       </c>
     </row>
@@ -7341,18 +7343,18 @@
       <c r="B210" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="C210" s="7">
+      <c r="C210" s="8">
         <v>307707.96100000001</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" s="6" t="s">
+      <c r="A211" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="B211" s="6" t="s">
+      <c r="B211" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="C211" s="7"/>
+      <c r="C211" s="8"/>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
@@ -7361,7 +7363,7 @@
       <c r="B212" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="C212" s="7">
+      <c r="C212" s="8">
         <v>153388.73000000001</v>
       </c>
     </row>
@@ -7372,18 +7374,18 @@
       <c r="B213" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="C213" s="7">
+      <c r="C213" s="8">
         <v>142656.459</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" s="6" t="s">
+      <c r="A214" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="B214" s="6" t="s">
+      <c r="B214" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="C214" s="7"/>
+      <c r="C214" s="8"/>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
@@ -7392,7 +7394,7 @@
       <c r="B215" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="C215" s="7">
+      <c r="C215" s="8">
         <v>384667.30499999999</v>
       </c>
     </row>
@@ -7403,18 +7405,18 @@
       <c r="B216" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="C216" s="7">
+      <c r="C216" s="8">
         <v>369284.87200000003</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" s="6" t="s">
+      <c r="A217" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="B217" s="6" t="s">
+      <c r="B217" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C217" s="7"/>
+      <c r="C217" s="8"/>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
@@ -7423,7 +7425,7 @@
       <c r="B218" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="C218" s="7">
+      <c r="C218" s="8">
         <v>275937.15600000002</v>
       </c>
     </row>
@@ -7434,7 +7436,7 @@
       <c r="B219" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="C219" s="7">
+      <c r="C219" s="8">
         <v>263781.93600000005</v>
       </c>
     </row>
@@ -7445,7 +7447,7 @@
       <c r="B220" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="C220" s="7">
+      <c r="C220" s="8">
         <v>194087.89400000003</v>
       </c>
     </row>
@@ -7456,7 +7458,7 @@
       <c r="B221" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="C221" s="7">
+      <c r="C221" s="8">
         <v>174435.80000000002</v>
       </c>
     </row>
@@ -7467,7 +7469,7 @@
       <c r="B222" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="C222" s="7">
+      <c r="C222" s="8">
         <v>177247.85100000002</v>
       </c>
     </row>
@@ -7478,7 +7480,7 @@
       <c r="B223" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="C223" s="7">
+      <c r="C223" s="8">
         <v>314676.68100000004</v>
       </c>
     </row>
@@ -7489,7 +7491,7 @@
       <c r="B224" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="C224" s="7">
+      <c r="C224" s="8">
         <v>305236.38200000004</v>
       </c>
     </row>
@@ -7500,7 +7502,7 @@
       <c r="B225" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="C225" s="7">
+      <c r="C225" s="8">
         <v>95195.133000000002</v>
       </c>
     </row>
@@ -7511,18 +7513,18 @@
       <c r="B226" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="C226" s="7">
+      <c r="C226" s="8">
         <v>88529.430000000008</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="6" t="s">
+      <c r="A227" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="B227" s="6" t="s">
+      <c r="B227" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="C227" s="7"/>
+      <c r="C227" s="8"/>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
@@ -7531,7 +7533,7 @@
       <c r="B228" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="C228" s="7">
+      <c r="C228" s="8">
         <v>105186.345</v>
       </c>
     </row>
@@ -7542,7 +7544,7 @@
       <c r="B229" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="C229" s="7">
+      <c r="C229" s="8">
         <v>97631.27</v>
       </c>
     </row>
@@ -7553,7 +7555,7 @@
       <c r="B230" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="C230" s="7">
+      <c r="C230" s="8">
         <v>106989.86320000001</v>
       </c>
     </row>
@@ -7564,7 +7566,7 @@
       <c r="B231" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="C231" s="7">
+      <c r="C231" s="8">
         <v>99568.766000000003</v>
       </c>
     </row>
@@ -7575,7 +7577,7 @@
       <c r="B232" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="C232" s="7">
+      <c r="C232" s="8">
         <v>135329.87600000002</v>
       </c>
     </row>
@@ -7586,7 +7588,7 @@
       <c r="B233" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C233" s="7">
+      <c r="C233" s="8">
         <v>121227.65490000001</v>
       </c>
     </row>
@@ -7597,7 +7599,7 @@
       <c r="B234" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="C234" s="7">
+      <c r="C234" s="8">
         <v>89456.631000000008</v>
       </c>
     </row>
@@ -7608,7 +7610,7 @@
       <c r="B235" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="C235" s="7">
+      <c r="C235" s="8">
         <v>82999.597999999998</v>
       </c>
     </row>
@@ -7619,7 +7621,7 @@
       <c r="B236" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="C236" s="7">
+      <c r="C236" s="8">
         <v>136038.48500000002</v>
       </c>
     </row>
@@ -7630,7 +7632,7 @@
       <c r="B237" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="C237" s="7">
+      <c r="C237" s="8">
         <v>129983.39200000001</v>
       </c>
     </row>
@@ -7641,7 +7643,7 @@
       <c r="B238" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="C238" s="7">
+      <c r="C238" s="8">
         <v>93694.59</v>
       </c>
     </row>
@@ -7652,7 +7654,7 @@
       <c r="B239" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="C239" s="7">
+      <c r="C239" s="8">
         <v>86968.550900000017</v>
       </c>
     </row>
@@ -7663,7 +7665,7 @@
       <c r="B240" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="C240" s="7">
+      <c r="C240" s="8">
         <v>74866.923999999999</v>
       </c>
     </row>
@@ -7674,7 +7676,7 @@
       <c r="B241" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="C241" s="7">
+      <c r="C241" s="8">
         <v>68976.127000000008</v>
       </c>
     </row>
@@ -7685,7 +7687,7 @@
       <c r="B242" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="C242" s="7">
+      <c r="C242" s="8">
         <v>131857.82500000001</v>
       </c>
     </row>
@@ -7696,7 +7698,7 @@
       <c r="B243" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="C243" s="7">
+      <c r="C243" s="8">
         <v>122390.93900000001</v>
       </c>
     </row>
@@ -7707,7 +7709,7 @@
       <c r="B244" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="C244" s="7">
+      <c r="C244" s="8">
         <v>0</v>
       </c>
     </row>
@@ -7718,7 +7720,7 @@
       <c r="B245" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="C245" s="7">
+      <c r="C245" s="8">
         <v>189433.10100000002</v>
       </c>
     </row>
@@ -7729,7 +7731,7 @@
       <c r="B246" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="C246" s="7">
+      <c r="C246" s="8">
         <v>166555.57600000003</v>
       </c>
     </row>
@@ -7740,7 +7742,7 @@
       <c r="B247" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="C247" s="7">
+      <c r="C247" s="8">
         <v>124585.01000000001</v>
       </c>
     </row>
@@ -7751,7 +7753,7 @@
       <c r="B248" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="C248" s="7">
+      <c r="C248" s="8">
         <v>133306.66800000001</v>
       </c>
     </row>
@@ -7762,7 +7764,7 @@
       <c r="B249" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="C249" s="7">
+      <c r="C249" s="8">
         <v>117257.42600000001</v>
       </c>
     </row>
@@ -7773,7 +7775,7 @@
       <c r="B250" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="C250" s="7">
+      <c r="C250" s="8">
         <v>125464.33900000002</v>
       </c>
     </row>
@@ -7784,7 +7786,7 @@
       <c r="B251" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="C251" s="7">
+      <c r="C251" s="8">
         <v>130507.54200000002</v>
       </c>
     </row>
@@ -7795,7 +7797,7 @@
       <c r="B252" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="C252" s="7">
+      <c r="C252" s="8">
         <v>121368.88500000001</v>
       </c>
     </row>
@@ -7806,7 +7808,7 @@
       <c r="B253" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="C253" s="7">
+      <c r="C253" s="8">
         <v>138616.32399999999</v>
       </c>
     </row>
@@ -7817,7 +7819,7 @@
       <c r="B254" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="C254" s="7">
+      <c r="C254" s="8">
         <v>131399.125</v>
       </c>
     </row>
@@ -7828,7 +7830,7 @@
       <c r="B255" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="C255" s="7">
+      <c r="C255" s="8">
         <v>146575.78100000002</v>
       </c>
     </row>
@@ -7839,7 +7841,7 @@
       <c r="B256" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="C256" s="7">
+      <c r="C256" s="8">
         <v>136311.63480000003</v>
       </c>
     </row>
@@ -7850,7 +7852,7 @@
       <c r="B257" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="C257" s="7">
+      <c r="C257" s="8">
         <v>151878.122</v>
       </c>
     </row>
@@ -7861,7 +7863,7 @@
       <c r="B258" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="C258" s="7">
+      <c r="C258" s="8">
         <v>138071.02100000001</v>
       </c>
     </row>
@@ -7872,7 +7874,7 @@
       <c r="B259" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="C259" s="7">
+      <c r="C259" s="8">
         <v>151878.122</v>
       </c>
     </row>
@@ -7883,7 +7885,7 @@
       <c r="B260" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="C260" s="7">
+      <c r="C260" s="8">
         <v>138071.02100000001</v>
       </c>
     </row>
@@ -7894,7 +7896,7 @@
       <c r="B261" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="C261" s="7">
+      <c r="C261" s="8">
         <v>0</v>
       </c>
     </row>
@@ -7905,18 +7907,18 @@
       <c r="B262" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="C262" s="7">
+      <c r="C262" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" s="6" t="s">
+      <c r="A263" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="B263" s="6" t="s">
+      <c r="B263" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="C263" s="7"/>
+      <c r="C263" s="8"/>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
@@ -7925,7 +7927,7 @@
       <c r="B264" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="C264" s="7">
+      <c r="C264" s="8">
         <v>111364.27500000001</v>
       </c>
     </row>
@@ -7936,7 +7938,7 @@
       <c r="B265" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="C265" s="7">
+      <c r="C265" s="8">
         <v>103364.75600000001</v>
       </c>
     </row>
@@ -7947,7 +7949,7 @@
       <c r="B266" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="C266" s="7">
+      <c r="C266" s="8">
         <v>134200.429</v>
       </c>
     </row>
@@ -7958,7 +7960,7 @@
       <c r="B267" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="C267" s="7">
+      <c r="C267" s="8">
         <v>124009.05</v>
       </c>
     </row>
@@ -7969,7 +7971,7 @@
       <c r="B268" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="C268" s="7">
+      <c r="C268" s="8">
         <v>110677.20400000001</v>
       </c>
     </row>
@@ -7980,7 +7982,7 @@
       <c r="B269" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="C269" s="7">
+      <c r="C269" s="8">
         <v>106211.53400000001</v>
       </c>
     </row>
@@ -7991,7 +7993,7 @@
       <c r="B270" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="C270" s="7">
+      <c r="C270" s="8">
         <v>156937.4455</v>
       </c>
     </row>
@@ -8002,7 +8004,7 @@
       <c r="B271" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="C271" s="7">
+      <c r="C271" s="8">
         <v>144057.133</v>
       </c>
     </row>
@@ -8013,7 +8015,7 @@
       <c r="B272" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="C272" s="7">
+      <c r="C272" s="8">
         <v>147847.89800000002</v>
       </c>
     </row>
@@ -8024,7 +8026,7 @@
       <c r="B273" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="C273" s="7">
+      <c r="C273" s="8">
         <v>132433.71460000001</v>
       </c>
     </row>
@@ -8035,7 +8037,7 @@
       <c r="B274" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C274" s="7">
+      <c r="C274" s="8">
         <v>109179.95000000001</v>
       </c>
     </row>
@@ -8046,7 +8048,7 @@
       <c r="B275" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="C275" s="7">
+      <c r="C275" s="8">
         <v>97796.776000000013</v>
       </c>
     </row>
@@ -8057,7 +8059,7 @@
       <c r="B276" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="C276" s="7">
+      <c r="C276" s="8">
         <v>167181.96000000002</v>
       </c>
     </row>
@@ -8068,7 +8070,7 @@
       <c r="B277" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="C277" s="7">
+      <c r="C277" s="8">
         <v>149751.67900000003</v>
       </c>
     </row>
@@ -8079,7 +8081,7 @@
       <c r="B278" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="C278" s="7">
+      <c r="C278" s="8">
         <v>86476.885000000009</v>
       </c>
     </row>
@@ -8090,7 +8092,7 @@
       <c r="B279" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="C279" s="7">
+      <c r="C279" s="8">
         <v>76404.031000000017</v>
       </c>
     </row>
@@ -8101,7 +8103,7 @@
       <c r="B280" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="C280" s="7">
+      <c r="C280" s="8">
         <v>135984.079</v>
       </c>
     </row>
@@ -8112,7 +8114,7 @@
       <c r="B281" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="C281" s="7">
+      <c r="C281" s="8">
         <v>125929.32</v>
       </c>
     </row>
@@ -8123,7 +8125,7 @@
       <c r="B282" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="C282" s="7">
+      <c r="C282" s="8">
         <v>129651.06000000001</v>
       </c>
     </row>
@@ -8134,7 +8136,7 @@
       <c r="B283" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="C283" s="7">
+      <c r="C283" s="8">
         <v>119427.5742</v>
       </c>
     </row>
@@ -8145,7 +8147,7 @@
       <c r="B284" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="C284" s="7">
+      <c r="C284" s="8">
         <v>158223.26740000001</v>
       </c>
     </row>
@@ -8156,7 +8158,7 @@
       <c r="B285" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="C285" s="7">
+      <c r="C285" s="8">
         <v>140232.91700000002</v>
       </c>
     </row>
@@ -8167,7 +8169,7 @@
       <c r="B286" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="C286" s="7">
+      <c r="C286" s="8">
         <v>132259.67700000003</v>
       </c>
     </row>
@@ -8178,7 +8180,7 @@
       <c r="B287" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="C287" s="7">
+      <c r="C287" s="8">
         <v>129363.65200000002</v>
       </c>
     </row>
@@ -8189,7 +8191,7 @@
       <c r="B288" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="C288" s="7">
+      <c r="C288" s="8">
         <v>313163.81800000003</v>
       </c>
     </row>
@@ -8200,7 +8202,7 @@
       <c r="B289" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="C289" s="7">
+      <c r="C289" s="8">
         <v>78381.930000000008</v>
       </c>
     </row>
@@ -8211,7 +8213,7 @@
       <c r="B290" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="C290" s="7">
+      <c r="C290" s="8">
         <v>189310.77000000002</v>
       </c>
     </row>
@@ -8222,7 +8224,7 @@
       <c r="B291" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="C291" s="7">
+      <c r="C291" s="8">
         <v>176054.516</v>
       </c>
     </row>
@@ -8233,7 +8235,7 @@
       <c r="B292" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="C292" s="7">
+      <c r="C292" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8244,18 +8246,18 @@
       <c r="B293" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="C293" s="7">
+      <c r="C293" s="8">
         <v>141285.826</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A294" s="6" t="s">
+      <c r="A294" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="B294" s="6" t="s">
+      <c r="B294" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="C294" s="7"/>
+      <c r="C294" s="8"/>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
@@ -8264,7 +8266,7 @@
       <c r="B295" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="C295" s="7">
+      <c r="C295" s="8">
         <v>93099.556000000011</v>
       </c>
     </row>
@@ -8275,7 +8277,7 @@
       <c r="B296" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="C296" s="7">
+      <c r="C296" s="8">
         <v>93099.556000000011</v>
       </c>
     </row>
@@ -8286,7 +8288,7 @@
       <c r="B297" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="C297" s="7">
+      <c r="C297" s="8">
         <v>285723.52600000001</v>
       </c>
     </row>
@@ -8297,7 +8299,7 @@
       <c r="B298" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="C298" s="7">
+      <c r="C298" s="8">
         <v>293477.10700000002</v>
       </c>
     </row>
@@ -8308,7 +8310,7 @@
       <c r="B299" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="C299" s="7">
+      <c r="C299" s="8">
         <v>274967.07700000005</v>
       </c>
     </row>
@@ -8319,7 +8321,7 @@
       <c r="B300" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="C300" s="7">
+      <c r="C300" s="8">
         <v>255717.63800000001</v>
       </c>
     </row>
@@ -8330,7 +8332,7 @@
       <c r="B301" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="C301" s="7">
+      <c r="C301" s="8">
         <v>242540.155</v>
       </c>
     </row>
@@ -8341,7 +8343,7 @@
       <c r="B302" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="C302" s="7">
+      <c r="C302" s="8">
         <v>227254.42300000001</v>
       </c>
     </row>
@@ -8352,7 +8354,7 @@
       <c r="B303" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="C303" s="7">
+      <c r="C303" s="8">
         <v>181381.23300000001</v>
       </c>
     </row>
@@ -8363,18 +8365,18 @@
       <c r="B304" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="C304" s="7">
+      <c r="C304" s="8">
         <v>510759.42500000005</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" s="6" t="s">
+      <c r="A305" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="B305" s="6" t="s">
+      <c r="B305" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="C305" s="7"/>
+      <c r="C305" s="8"/>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
@@ -8383,7 +8385,7 @@
       <c r="B306" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="C306" s="7">
+      <c r="C306" s="8">
         <v>132123.60700000002</v>
       </c>
     </row>
@@ -8394,7 +8396,7 @@
       <c r="B307" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="C307" s="7">
+      <c r="C307" s="8">
         <v>122639.37400000001</v>
       </c>
     </row>
@@ -8405,7 +8407,7 @@
       <c r="B308" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="C308" s="7">
+      <c r="C308" s="8">
         <v>196179.90700000001</v>
       </c>
     </row>
@@ -8416,7 +8418,7 @@
       <c r="B309" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="C309" s="7">
+      <c r="C309" s="8">
         <v>182449.74000000002</v>
       </c>
     </row>
@@ -8427,18 +8429,18 @@
       <c r="B310" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="C310" s="7">
+      <c r="C310" s="8">
         <v>191590.24500000002</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311" s="6" t="s">
+      <c r="A311" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="B311" s="6" t="s">
+      <c r="B311" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="C311" s="7"/>
+      <c r="C311" s="8"/>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
@@ -8447,7 +8449,7 @@
       <c r="B312" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="C312" s="7">
+      <c r="C312" s="8">
         <v>157075.49000000002</v>
       </c>
     </row>
@@ -8458,7 +8460,7 @@
       <c r="B313" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="C313" s="7">
+      <c r="C313" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8469,7 +8471,7 @@
       <c r="B314" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="C314" s="7">
+      <c r="C314" s="8">
         <v>145804.79540000003</v>
       </c>
     </row>
@@ -8480,7 +8482,7 @@
       <c r="B315" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="C315" s="7">
+      <c r="C315" s="8">
         <v>214746.29</v>
       </c>
     </row>
@@ -8491,7 +8493,7 @@
       <c r="B316" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="C316" s="7">
+      <c r="C316" s="8">
         <v>202022.39200000002</v>
       </c>
     </row>
@@ -8502,7 +8504,7 @@
       <c r="B317" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="C317" s="7">
+      <c r="C317" s="8">
         <v>198757.90000000002</v>
       </c>
     </row>
@@ -8513,7 +8515,7 @@
       <c r="B318" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="C318" s="7">
+      <c r="C318" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8524,7 +8526,7 @@
       <c r="B319" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="C319" s="7">
+      <c r="C319" s="8">
         <v>194174.86000000002</v>
       </c>
     </row>
@@ -8535,7 +8537,7 @@
       <c r="B320" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="C320" s="7">
+      <c r="C320" s="8">
         <v>164174.86800000002</v>
       </c>
     </row>
@@ -8546,7 +8548,7 @@
       <c r="B321" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="C321" s="7">
+      <c r="C321" s="8">
         <v>156384.09599999999</v>
       </c>
     </row>
@@ -8557,7 +8559,7 @@
       <c r="B322" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="C322" s="7">
+      <c r="C322" s="8">
         <v>159614.48800000001</v>
       </c>
     </row>
@@ -8568,7 +8570,7 @@
       <c r="B323" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="C323" s="7">
+      <c r="C323" s="8">
         <v>184212.38</v>
       </c>
     </row>
@@ -8579,18 +8581,18 @@
       <c r="B324" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="C324" s="7">
+      <c r="C324" s="8">
         <v>504084.10800000007</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A325" s="6" t="s">
+      <c r="A325" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="B325" s="6" t="s">
+      <c r="B325" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="C325" s="7"/>
+      <c r="C325" s="8"/>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="4" t="s">
@@ -8599,7 +8601,7 @@
       <c r="B326" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="C326" s="7">
+      <c r="C326" s="8">
         <v>171761.29300000001</v>
       </c>
     </row>
@@ -8610,7 +8612,7 @@
       <c r="B327" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="C327" s="7">
+      <c r="C327" s="8">
         <v>159436.99200000003</v>
       </c>
     </row>
@@ -8621,7 +8623,7 @@
       <c r="B328" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="C328" s="7">
+      <c r="C328" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8632,7 +8634,7 @@
       <c r="B329" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="C329" s="7">
+      <c r="C329" s="8">
         <v>106565.42600000001</v>
       </c>
     </row>
@@ -8643,7 +8645,7 @@
       <c r="B330" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="C330" s="7">
+      <c r="C330" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8654,7 +8656,7 @@
       <c r="B331" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="C331" s="7">
+      <c r="C331" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8665,7 +8667,7 @@
       <c r="B332" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="C332" s="7">
+      <c r="C332" s="8">
         <v>114302.08900000002</v>
       </c>
     </row>
@@ -8676,18 +8678,18 @@
       <c r="B333" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="C333" s="7">
+      <c r="C333" s="8">
         <v>106297.895</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A334" s="6" t="s">
+      <c r="A334" s="5" t="s">
         <v>661</v>
       </c>
-      <c r="B334" s="6" t="s">
+      <c r="B334" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="C334" s="7"/>
+      <c r="C334" s="8"/>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="4" t="s">
@@ -8696,7 +8698,7 @@
       <c r="B335" s="4" t="s">
         <v>664</v>
       </c>
-      <c r="C335" s="7">
+      <c r="C335" s="8">
         <v>184862.32600000003</v>
       </c>
     </row>
@@ -8707,18 +8709,18 @@
       <c r="B336" s="4" t="s">
         <v>666</v>
       </c>
-      <c r="C336" s="7">
+      <c r="C336" s="8">
         <v>171598.43799999999</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A337" s="6" t="s">
+      <c r="A337" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="B337" s="6" t="s">
+      <c r="B337" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="C337" s="7"/>
+      <c r="C337" s="8"/>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="4" t="s">
@@ -8727,7 +8729,7 @@
       <c r="B338" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="C338" s="7">
+      <c r="C338" s="8">
         <v>124913.008</v>
       </c>
     </row>
@@ -8738,7 +8740,7 @@
       <c r="B339" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="C339" s="7">
+      <c r="C339" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8749,18 +8751,18 @@
       <c r="B340" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="C340" s="7">
+      <c r="C340" s="8">
         <v>116164.97200000001</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A341" s="6" t="s">
+      <c r="A341" s="5" t="s">
         <v>675</v>
       </c>
-      <c r="B341" s="6" t="s">
+      <c r="B341" s="5" t="s">
         <v>676</v>
       </c>
-      <c r="C341" s="7"/>
+      <c r="C341" s="8"/>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="4" t="s">
@@ -8769,7 +8771,7 @@
       <c r="B342" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="C342" s="7">
+      <c r="C342" s="8">
         <v>369258.89000000007</v>
       </c>
     </row>
@@ -8780,18 +8782,18 @@
       <c r="B343" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="C343" s="7">
+      <c r="C343" s="8">
         <v>338508.06</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A344" s="6" t="s">
+      <c r="A344" s="5" t="s">
         <v>681</v>
       </c>
-      <c r="B344" s="6" t="s">
+      <c r="B344" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="C344" s="7"/>
+      <c r="C344" s="8"/>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" s="4" t="s">
@@ -8800,7 +8802,7 @@
       <c r="B345" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="C345" s="7">
+      <c r="C345" s="8">
         <v>461566.62200000003</v>
       </c>
     </row>
@@ -8811,18 +8813,18 @@
       <c r="B346" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="C346" s="7">
+      <c r="C346" s="8">
         <v>446197.66400000005</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A347" s="6" t="s">
+      <c r="A347" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="B347" s="6" t="s">
+      <c r="B347" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="C347" s="7"/>
+      <c r="C347" s="8"/>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" s="4" t="s">
@@ -8831,18 +8833,18 @@
       <c r="B348" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="C348" s="7">
+      <c r="C348" s="8">
         <v>226367.53700000004</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A349" s="6" t="s">
+      <c r="A349" s="5" t="s">
         <v>691</v>
       </c>
-      <c r="B349" s="6" t="s">
+      <c r="B349" s="5" t="s">
         <v>692</v>
       </c>
-      <c r="C349" s="7"/>
+      <c r="C349" s="8"/>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" s="4" t="s">
@@ -8851,18 +8853,18 @@
       <c r="B350" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="C350" s="7">
+      <c r="C350" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A351" s="6" t="s">
+      <c r="A351" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="B351" s="6" t="s">
+      <c r="B351" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="C351" s="7"/>
+      <c r="C351" s="8"/>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" s="4" t="s">
@@ -8871,7 +8873,7 @@
       <c r="B352" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="C352" s="7">
+      <c r="C352" s="8">
         <v>245340.84080000001</v>
       </c>
     </row>
@@ -8882,7 +8884,7 @@
       <c r="B353" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="C353" s="7">
+      <c r="C353" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8893,18 +8895,18 @@
       <c r="B354" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="C354" s="7">
+      <c r="C354" s="8">
         <v>228160.38300000003</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A355" s="6" t="s">
+      <c r="A355" s="5" t="s">
         <v>703</v>
       </c>
-      <c r="B355" s="6" t="s">
+      <c r="B355" s="5" t="s">
         <v>704</v>
       </c>
-      <c r="C355" s="7"/>
+      <c r="C355" s="8"/>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
@@ -8913,7 +8915,7 @@
       <c r="B356" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="C356" s="7">
+      <c r="C356" s="8">
         <v>301793.66800000001</v>
       </c>
     </row>
@@ -8924,18 +8926,18 @@
       <c r="B357" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="C357" s="7">
+      <c r="C357" s="8">
         <v>280662.77800000005</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A358" s="6" t="s">
+      <c r="A358" s="5" t="s">
         <v>709</v>
       </c>
-      <c r="B358" s="6" t="s">
+      <c r="B358" s="5" t="s">
         <v>710</v>
       </c>
-      <c r="C358" s="7"/>
+      <c r="C358" s="8"/>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
@@ -8944,18 +8946,18 @@
       <c r="B359" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="C359" s="7">
+      <c r="C359" s="8">
         <v>180257.52800000002</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A360" s="6" t="s">
+      <c r="A360" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="B360" s="6" t="s">
+      <c r="B360" s="5" t="s">
         <v>714</v>
       </c>
-      <c r="C360" s="7"/>
+      <c r="C360" s="8"/>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
@@ -8964,7 +8966,7 @@
       <c r="B361" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="C361" s="7">
+      <c r="C361" s="8">
         <v>609100.91</v>
       </c>
     </row>
@@ -8975,18 +8977,18 @@
       <c r="B362" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="C362" s="7">
+      <c r="C362" s="8">
         <v>566447.54100000008</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A363" s="6" t="s">
+      <c r="A363" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="B363" s="6" t="s">
+      <c r="B363" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="C363" s="7"/>
+      <c r="C363" s="8"/>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" s="4" t="s">
@@ -8995,18 +8997,18 @@
       <c r="B364" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="C364" s="7">
+      <c r="C364" s="8">
         <v>46078.538000000008</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A365" s="6" t="s">
+      <c r="A365" s="5" t="s">
         <v>723</v>
       </c>
-      <c r="B365" s="6" t="s">
+      <c r="B365" s="5" t="s">
         <v>724</v>
       </c>
-      <c r="C365" s="7"/>
+      <c r="C365" s="8"/>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" s="4" t="s">
@@ -9015,18 +9017,18 @@
       <c r="B366" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="C366" s="7">
+      <c r="C366" s="8">
         <v>565918.63900000008</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A367" s="6" t="s">
+      <c r="A367" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="B367" s="6" t="s">
+      <c r="B367" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="C367" s="7"/>
+      <c r="C367" s="8"/>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" s="4" t="s">
@@ -9035,7 +9037,7 @@
       <c r="B368" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="C368" s="7">
+      <c r="C368" s="8">
         <v>97267.555000000008</v>
       </c>
     </row>
@@ -9046,7 +9048,7 @@
       <c r="B369" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="C369" s="7">
+      <c r="C369" s="8">
         <v>74328.782000000007</v>
       </c>
     </row>
@@ -9057,7 +9059,7 @@
       <c r="B370" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="C370" s="7">
+      <c r="C370" s="8">
         <v>334404.34500000003</v>
       </c>
     </row>
@@ -9068,7 +9070,7 @@
       <c r="B371" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="C371" s="7">
+      <c r="C371" s="8">
         <v>125147.48400000001</v>
       </c>
     </row>
@@ -9079,7 +9081,7 @@
       <c r="B372" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="C372" s="7">
+      <c r="C372" s="8">
         <v>226197.89500000002</v>
       </c>
     </row>
@@ -9090,7 +9092,7 @@
       <c r="B373" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="C373" s="7">
+      <c r="C373" s="8">
         <v>115195.15700000001</v>
       </c>
     </row>
@@ -9101,7 +9103,7 @@
       <c r="B374" s="4" t="s">
         <v>742</v>
       </c>
-      <c r="C374" s="7">
+      <c r="C374" s="8">
         <v>235701.114</v>
       </c>
     </row>
@@ -9112,18 +9114,18 @@
       <c r="B375" s="4" t="s">
         <v>744</v>
       </c>
-      <c r="C375" s="7">
+      <c r="C375" s="8">
         <v>204781.50000000003</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A376" s="6" t="s">
+      <c r="A376" s="5" t="s">
         <v>745</v>
       </c>
-      <c r="B376" s="6" t="s">
+      <c r="B376" s="5" t="s">
         <v>746</v>
       </c>
-      <c r="C376" s="7"/>
+      <c r="C376" s="8"/>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" s="4" t="s">
@@ -9132,7 +9134,7 @@
       <c r="B377" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="C377" s="7">
+      <c r="C377" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9143,7 +9145,7 @@
       <c r="B378" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="C378" s="7">
+      <c r="C378" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9154,7 +9156,7 @@
       <c r="B379" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="C379" s="7">
+      <c r="C379" s="8">
         <v>245626.73300000001</v>
       </c>
     </row>
@@ -9165,7 +9167,7 @@
       <c r="B380" s="4" t="s">
         <v>754</v>
       </c>
-      <c r="C380" s="7">
+      <c r="C380" s="8">
         <v>245626.53500000003</v>
       </c>
     </row>
@@ -9176,7 +9178,7 @@
       <c r="B381" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="C381" s="7">
+      <c r="C381" s="8">
         <v>243945.77900000004</v>
       </c>
     </row>
@@ -9187,7 +9189,7 @@
       <c r="B382" s="4" t="s">
         <v>758</v>
       </c>
-      <c r="C382" s="7">
+      <c r="C382" s="8">
         <v>243945.77900000004</v>
       </c>
     </row>
@@ -9198,7 +9200,7 @@
       <c r="B383" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="C383" s="7">
+      <c r="C383" s="8">
         <v>245851.61700000003</v>
       </c>
     </row>
@@ -9209,7 +9211,7 @@
       <c r="B384" s="4" t="s">
         <v>762</v>
       </c>
-      <c r="C384" s="7">
+      <c r="C384" s="8">
         <v>245851.61700000003</v>
       </c>
     </row>
@@ -9220,7 +9222,7 @@
       <c r="B385" s="4" t="s">
         <v>764</v>
       </c>
-      <c r="C385" s="7">
+      <c r="C385" s="8">
         <v>263454.26800000004</v>
       </c>
     </row>
@@ -9231,7 +9233,7 @@
       <c r="B386" s="4" t="s">
         <v>766</v>
       </c>
-      <c r="C386" s="7">
+      <c r="C386" s="8">
         <v>284312.71000000002</v>
       </c>
     </row>
@@ -9242,7 +9244,7 @@
       <c r="B387" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="C387" s="7">
+      <c r="C387" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9253,18 +9255,18 @@
       <c r="B388" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="C388" s="7">
+      <c r="C388" s="8">
         <v>284312.71000000002</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A389" s="6" t="s">
+      <c r="A389" s="5" t="s">
         <v>771</v>
       </c>
-      <c r="B389" s="6" t="s">
+      <c r="B389" s="5" t="s">
         <v>772</v>
       </c>
-      <c r="C389" s="7"/>
+      <c r="C389" s="8"/>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" s="4" t="s">
@@ -9273,7 +9275,7 @@
       <c r="B390" s="4" t="s">
         <v>774</v>
       </c>
-      <c r="C390" s="7">
+      <c r="C390" s="8">
         <v>235033.348</v>
       </c>
     </row>
@@ -9284,7 +9286,7 @@
       <c r="B391" s="4" t="s">
         <v>776</v>
       </c>
-      <c r="C391" s="7">
+      <c r="C391" s="8">
         <v>187793.89200000002</v>
       </c>
     </row>
@@ -9295,7 +9297,7 @@
       <c r="B392" s="4" t="s">
         <v>778</v>
       </c>
-      <c r="C392" s="7">
+      <c r="C392" s="8">
         <v>235033.348</v>
       </c>
     </row>
@@ -9306,7 +9308,7 @@
       <c r="B393" s="4" t="s">
         <v>780</v>
       </c>
-      <c r="C393" s="7">
+      <c r="C393" s="8">
         <v>187793.89200000002</v>
       </c>
     </row>
@@ -9317,7 +9319,7 @@
       <c r="B394" s="4" t="s">
         <v>782</v>
       </c>
-      <c r="C394" s="7">
+      <c r="C394" s="8">
         <v>477206.98300000007</v>
       </c>
     </row>
@@ -9328,18 +9330,18 @@
       <c r="B395" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="C395" s="7">
+      <c r="C395" s="8">
         <v>477206.98300000007</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A396" s="6" t="s">
+      <c r="A396" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="B396" s="6" t="s">
+      <c r="B396" s="5" t="s">
         <v>786</v>
       </c>
-      <c r="C396" s="7"/>
+      <c r="C396" s="8"/>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" s="4" t="s">
@@ -9348,7 +9350,7 @@
       <c r="B397" s="4" t="s">
         <v>788</v>
       </c>
-      <c r="C397" s="7">
+      <c r="C397" s="8">
         <v>206729.66600000003</v>
       </c>
     </row>
@@ -9359,7 +9361,7 @@
       <c r="B398" s="4" t="s">
         <v>790</v>
       </c>
-      <c r="C398" s="7">
+      <c r="C398" s="8">
         <v>206729.66600000003</v>
       </c>
     </row>
@@ -9370,7 +9372,7 @@
       <c r="B399" s="4" t="s">
         <v>792</v>
       </c>
-      <c r="C399" s="7">
+      <c r="C399" s="8">
         <v>206729.66600000003</v>
       </c>
     </row>
@@ -9381,7 +9383,7 @@
       <c r="B400" s="4" t="s">
         <v>794</v>
       </c>
-      <c r="C400" s="7">
+      <c r="C400" s="8">
         <v>206729.66600000003</v>
       </c>
     </row>
@@ -9392,7 +9394,7 @@
       <c r="B401" s="4" t="s">
         <v>796</v>
       </c>
-      <c r="C401" s="7">
+      <c r="C401" s="8">
         <v>225817.95500000002</v>
       </c>
     </row>
@@ -9403,18 +9405,18 @@
       <c r="B402" s="4" t="s">
         <v>798</v>
       </c>
-      <c r="C402" s="7">
+      <c r="C402" s="8">
         <v>225817.94400000002</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A403" s="6" t="s">
+      <c r="A403" s="5" t="s">
         <v>799</v>
       </c>
-      <c r="B403" s="6" t="s">
+      <c r="B403" s="5" t="s">
         <v>800</v>
       </c>
-      <c r="C403" s="7"/>
+      <c r="C403" s="8"/>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="4" t="s">
@@ -9423,7 +9425,7 @@
       <c r="B404" s="4" t="s">
         <v>802</v>
       </c>
-      <c r="C404" s="7">
+      <c r="C404" s="8">
         <v>247607.40400000004</v>
       </c>
     </row>
@@ -9434,7 +9436,7 @@
       <c r="B405" s="4" t="s">
         <v>804</v>
       </c>
-      <c r="C405" s="7">
+      <c r="C405" s="8">
         <v>196239.25200000004</v>
       </c>
     </row>
@@ -9445,7 +9447,7 @@
       <c r="B406" s="4" t="s">
         <v>806</v>
       </c>
-      <c r="C406" s="7">
+      <c r="C406" s="8">
         <v>247607.40400000004</v>
       </c>
     </row>
@@ -9456,7 +9458,7 @@
       <c r="B407" s="4" t="s">
         <v>808</v>
       </c>
-      <c r="C407" s="7">
+      <c r="C407" s="8">
         <v>196239.25200000004</v>
       </c>
     </row>
@@ -9467,7 +9469,7 @@
       <c r="B408" s="4" t="s">
         <v>810</v>
       </c>
-      <c r="C408" s="7">
+      <c r="C408" s="8">
         <v>233516.272</v>
       </c>
     </row>
@@ -9478,7 +9480,7 @@
       <c r="B409" s="4" t="s">
         <v>812</v>
       </c>
-      <c r="C409" s="7">
+      <c r="C409" s="8">
         <v>185071.39200000002</v>
       </c>
     </row>
@@ -9489,7 +9491,7 @@
       <c r="B410" s="4" t="s">
         <v>814</v>
       </c>
-      <c r="C410" s="7">
+      <c r="C410" s="8">
         <v>233516.272</v>
       </c>
     </row>
@@ -9500,18 +9502,18 @@
       <c r="B411" s="4" t="s">
         <v>816</v>
       </c>
-      <c r="C411" s="7">
+      <c r="C411" s="8">
         <v>185071.39200000002</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A412" s="6" t="s">
+      <c r="A412" s="5" t="s">
         <v>817</v>
       </c>
-      <c r="B412" s="6" t="s">
+      <c r="B412" s="5" t="s">
         <v>818</v>
       </c>
-      <c r="C412" s="7"/>
+      <c r="C412" s="8"/>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" s="4" t="s">
@@ -9520,7 +9522,7 @@
       <c r="B413" s="4" t="s">
         <v>820</v>
       </c>
-      <c r="C413" s="7">
+      <c r="C413" s="8">
         <v>283683.03700000001</v>
       </c>
     </row>
@@ -9531,7 +9533,7 @@
       <c r="B414" s="4" t="s">
         <v>822</v>
       </c>
-      <c r="C414" s="7">
+      <c r="C414" s="8">
         <v>276638.76900000003</v>
       </c>
     </row>
@@ -9542,7 +9544,7 @@
       <c r="B415" s="4" t="s">
         <v>824</v>
       </c>
-      <c r="C415" s="7">
+      <c r="C415" s="8">
         <v>283683.03700000001</v>
       </c>
     </row>
@@ -9553,7 +9555,7 @@
       <c r="B416" s="4" t="s">
         <v>826</v>
       </c>
-      <c r="C416" s="7">
+      <c r="C416" s="8">
         <v>276638.76900000003</v>
       </c>
     </row>
@@ -9564,7 +9566,7 @@
       <c r="B417" s="4" t="s">
         <v>828</v>
       </c>
-      <c r="C417" s="7">
+      <c r="C417" s="8">
         <v>229023.34400000004</v>
       </c>
     </row>
@@ -9575,7 +9577,7 @@
       <c r="B418" s="4" t="s">
         <v>830</v>
       </c>
-      <c r="C418" s="7">
+      <c r="C418" s="8">
         <v>338850.73200000002</v>
       </c>
     </row>
@@ -9586,7 +9588,7 @@
       <c r="B419" s="4" t="s">
         <v>832</v>
       </c>
-      <c r="C419" s="7">
+      <c r="C419" s="8">
         <v>337230.83900000004</v>
       </c>
     </row>
@@ -9597,7 +9599,7 @@
       <c r="B420" s="4" t="s">
         <v>834</v>
       </c>
-      <c r="C420" s="7">
+      <c r="C420" s="8">
         <v>338850.73200000002</v>
       </c>
     </row>
@@ -9608,7 +9610,7 @@
       <c r="B421" s="4" t="s">
         <v>836</v>
       </c>
-      <c r="C421" s="7">
+      <c r="C421" s="8">
         <v>337230.83900000004</v>
       </c>
     </row>
@@ -9619,7 +9621,7 @@
       <c r="B422" s="4" t="s">
         <v>838</v>
       </c>
-      <c r="C422" s="7">
+      <c r="C422" s="8">
         <v>308233.70600000006</v>
       </c>
     </row>
@@ -9630,7 +9632,7 @@
       <c r="B423" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="C423" s="7">
+      <c r="C423" s="8">
         <v>308233.70600000006</v>
       </c>
     </row>
@@ -9641,7 +9643,7 @@
       <c r="B424" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="C424" s="7">
+      <c r="C424" s="8">
         <v>341398.10100000002</v>
       </c>
     </row>
@@ -9652,18 +9654,18 @@
       <c r="B425" s="4" t="s">
         <v>844</v>
       </c>
-      <c r="C425" s="7">
+      <c r="C425" s="8">
         <v>341398.10100000002</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A426" s="6" t="s">
+      <c r="A426" s="5" t="s">
         <v>845</v>
       </c>
-      <c r="B426" s="6" t="s">
+      <c r="B426" s="5" t="s">
         <v>846</v>
       </c>
-      <c r="C426" s="7"/>
+      <c r="C426" s="8"/>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" s="4" t="s">
@@ -9672,7 +9674,7 @@
       <c r="B427" s="4" t="s">
         <v>848</v>
       </c>
-      <c r="C427" s="7">
+      <c r="C427" s="8">
         <v>221289.71700000003</v>
       </c>
     </row>
@@ -9683,7 +9685,7 @@
       <c r="B428" s="4" t="s">
         <v>850</v>
       </c>
-      <c r="C428" s="7">
+      <c r="C428" s="8">
         <v>221289.71700000003</v>
       </c>
     </row>
@@ -9694,7 +9696,7 @@
       <c r="B429" s="4" t="s">
         <v>852</v>
       </c>
-      <c r="C429" s="7">
+      <c r="C429" s="8">
         <v>221289.71700000003</v>
       </c>
     </row>
@@ -9705,7 +9707,7 @@
       <c r="B430" s="4" t="s">
         <v>854</v>
       </c>
-      <c r="C430" s="7">
+      <c r="C430" s="8">
         <v>221289.71700000003</v>
       </c>
     </row>
@@ -9716,7 +9718,7 @@
       <c r="B431" s="4" t="s">
         <v>856</v>
       </c>
-      <c r="C431" s="7">
+      <c r="C431" s="8">
         <v>426304.92300000001</v>
       </c>
     </row>
@@ -9727,18 +9729,18 @@
       <c r="B432" s="4" t="s">
         <v>858</v>
       </c>
-      <c r="C432" s="7">
+      <c r="C432" s="8">
         <v>237348.71600000001</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A433" s="6" t="s">
+      <c r="A433" s="5" t="s">
         <v>859</v>
       </c>
-      <c r="B433" s="6" t="s">
+      <c r="B433" s="5" t="s">
         <v>860</v>
       </c>
-      <c r="C433" s="7"/>
+      <c r="C433" s="8"/>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" s="4" t="s">
@@ -9747,7 +9749,7 @@
       <c r="B434" s="4" t="s">
         <v>862</v>
       </c>
-      <c r="C434" s="7">
+      <c r="C434" s="8">
         <v>246707.01000000004</v>
       </c>
     </row>
@@ -9758,7 +9760,7 @@
       <c r="B435" s="4" t="s">
         <v>864</v>
       </c>
-      <c r="C435" s="7">
+      <c r="C435" s="8">
         <v>218303.80000000002</v>
       </c>
     </row>
@@ -9769,7 +9771,7 @@
       <c r="B436" s="4" t="s">
         <v>866</v>
       </c>
-      <c r="C436" s="7">
+      <c r="C436" s="8">
         <v>246707.01000000004</v>
       </c>
     </row>
@@ -9780,7 +9782,7 @@
       <c r="B437" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="C437" s="7">
+      <c r="C437" s="8">
         <v>218303.80000000002</v>
       </c>
     </row>
@@ -9791,7 +9793,7 @@
       <c r="B438" s="4" t="s">
         <v>870</v>
       </c>
-      <c r="C438" s="7">
+      <c r="C438" s="8">
         <v>208224.32400000002</v>
       </c>
     </row>
@@ -9802,7 +9804,7 @@
       <c r="B439" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="C439" s="7">
+      <c r="C439" s="8">
         <v>195942.19700000001</v>
       </c>
     </row>
@@ -9813,7 +9815,7 @@
       <c r="B440" s="4" t="s">
         <v>874</v>
       </c>
-      <c r="C440" s="7">
+      <c r="C440" s="8">
         <v>208224.32400000002</v>
       </c>
     </row>
@@ -9824,7 +9826,7 @@
       <c r="B441" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="C441" s="7">
+      <c r="C441" s="8">
         <v>208224.32400000002</v>
       </c>
     </row>
@@ -9835,18 +9837,18 @@
       <c r="B442" s="4" t="s">
         <v>878</v>
       </c>
-      <c r="C442" s="7">
+      <c r="C442" s="8">
         <v>208224.32400000002</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A443" s="6" t="s">
+      <c r="A443" s="5" t="s">
         <v>879</v>
       </c>
-      <c r="B443" s="6" t="s">
+      <c r="B443" s="5" t="s">
         <v>880</v>
       </c>
-      <c r="C443" s="7"/>
+      <c r="C443" s="8"/>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" s="4" t="s">
@@ -9855,7 +9857,7 @@
       <c r="B444" s="4" t="s">
         <v>882</v>
       </c>
-      <c r="C444" s="7">
+      <c r="C444" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9866,7 +9868,7 @@
       <c r="B445" s="4" t="s">
         <v>884</v>
       </c>
-      <c r="C445" s="7">
+      <c r="C445" s="8">
         <v>264114.565</v>
       </c>
     </row>
@@ -9877,7 +9879,7 @@
       <c r="B446" s="4" t="s">
         <v>886</v>
       </c>
-      <c r="C446" s="7">
+      <c r="C446" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9888,7 +9890,7 @@
       <c r="B447" s="4" t="s">
         <v>888</v>
       </c>
-      <c r="C447" s="7">
+      <c r="C447" s="8">
         <v>264114.565</v>
       </c>
     </row>
@@ -9899,7 +9901,7 @@
       <c r="B448" s="4" t="s">
         <v>890</v>
       </c>
-      <c r="C448" s="7">
+      <c r="C448" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9910,7 +9912,7 @@
       <c r="B449" s="4" t="s">
         <v>892</v>
       </c>
-      <c r="C449" s="7">
+      <c r="C449" s="8">
         <v>234101.538</v>
       </c>
     </row>
@@ -9921,7 +9923,7 @@
       <c r="B450" s="4" t="s">
         <v>894</v>
       </c>
-      <c r="C450" s="7">
+      <c r="C450" s="8">
         <v>245868.98600000003</v>
       </c>
     </row>
@@ -9932,7 +9934,7 @@
       <c r="B451" s="4" t="s">
         <v>896</v>
       </c>
-      <c r="C451" s="7">
+      <c r="C451" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9943,7 +9945,7 @@
       <c r="B452" s="4" t="s">
         <v>898</v>
       </c>
-      <c r="C452" s="7">
+      <c r="C452" s="8">
         <v>234101.538</v>
       </c>
     </row>
@@ -9954,7 +9956,7 @@
       <c r="B453" s="4" t="s">
         <v>900</v>
       </c>
-      <c r="C453" s="7">
+      <c r="C453" s="8">
         <v>245868.98600000003</v>
       </c>
     </row>
@@ -9965,7 +9967,7 @@
       <c r="B454" s="4" t="s">
         <v>902</v>
       </c>
-      <c r="C454" s="7">
+      <c r="C454" s="8">
         <v>332842.34500000003</v>
       </c>
     </row>
@@ -9976,18 +9978,18 @@
       <c r="B455" s="4" t="s">
         <v>904</v>
       </c>
-      <c r="C455" s="7">
+      <c r="C455" s="8">
         <v>332842.34500000003</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A456" s="6" t="s">
+      <c r="A456" s="5" t="s">
         <v>905</v>
       </c>
-      <c r="B456" s="6" t="s">
+      <c r="B456" s="5" t="s">
         <v>906</v>
       </c>
-      <c r="C456" s="7"/>
+      <c r="C456" s="8"/>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" s="4" t="s">
@@ -9996,7 +9998,7 @@
       <c r="B457" s="4" t="s">
         <v>908</v>
       </c>
-      <c r="C457" s="7">
+      <c r="C457" s="8">
         <v>274920.31599999999</v>
       </c>
     </row>
@@ -10007,7 +10009,7 @@
       <c r="B458" s="4" t="s">
         <v>910</v>
       </c>
-      <c r="C458" s="7">
+      <c r="C458" s="8">
         <v>250470.85800000001</v>
       </c>
     </row>
@@ -10018,7 +10020,7 @@
       <c r="B459" s="4" t="s">
         <v>912</v>
       </c>
-      <c r="C459" s="7">
+      <c r="C459" s="8">
         <v>256211.09800000003</v>
       </c>
     </row>
@@ -10029,7 +10031,7 @@
       <c r="B460" s="4" t="s">
         <v>914</v>
       </c>
-      <c r="C460" s="7">
+      <c r="C460" s="8">
         <v>274920.31599999999</v>
       </c>
     </row>
@@ -10040,7 +10042,7 @@
       <c r="B461" s="4" t="s">
         <v>916</v>
       </c>
-      <c r="C461" s="7">
+      <c r="C461" s="8">
         <v>250470.85800000001</v>
       </c>
     </row>
@@ -10051,7 +10053,7 @@
       <c r="B462" s="4" t="s">
         <v>918</v>
       </c>
-      <c r="C462" s="7">
+      <c r="C462" s="8">
         <v>256198.80000000002</v>
       </c>
     </row>
@@ -10062,7 +10064,7 @@
       <c r="B463" s="4" t="s">
         <v>920</v>
       </c>
-      <c r="C463" s="7">
+      <c r="C463" s="8">
         <v>246568.46500000003</v>
       </c>
     </row>
@@ -10073,7 +10075,7 @@
       <c r="B464" s="4" t="s">
         <v>922</v>
       </c>
-      <c r="C464" s="7">
+      <c r="C464" s="8">
         <v>238607.08300000001</v>
       </c>
     </row>
@@ -10084,7 +10086,7 @@
       <c r="B465" s="4" t="s">
         <v>924</v>
       </c>
-      <c r="C465" s="7">
+      <c r="C465" s="8">
         <v>230992.92700000003</v>
       </c>
     </row>
@@ -10095,7 +10097,7 @@
       <c r="B466" s="4" t="s">
         <v>926</v>
       </c>
-      <c r="C466" s="7">
+      <c r="C466" s="8">
         <v>246568.46500000003</v>
       </c>
     </row>
@@ -10106,7 +10108,7 @@
       <c r="B467" s="4" t="s">
         <v>928</v>
       </c>
-      <c r="C467" s="7">
+      <c r="C467" s="8">
         <v>237408.19300000003</v>
       </c>
     </row>
@@ -10117,7 +10119,7 @@
       <c r="B468" s="4" t="s">
         <v>930</v>
       </c>
-      <c r="C468" s="7">
+      <c r="C468" s="8">
         <v>230992.92700000003</v>
       </c>
     </row>
@@ -10128,7 +10130,7 @@
       <c r="B469" s="4" t="s">
         <v>932</v>
       </c>
-      <c r="C469" s="7">
+      <c r="C469" s="8">
         <v>246566.74900000001</v>
       </c>
     </row>
@@ -10139,7 +10141,7 @@
       <c r="B470" s="4" t="s">
         <v>934</v>
       </c>
-      <c r="C470" s="7">
+      <c r="C470" s="8">
         <v>246566.74900000001</v>
       </c>
     </row>
@@ -10150,7 +10152,7 @@
       <c r="B471" s="4" t="s">
         <v>936</v>
       </c>
-      <c r="C471" s="7">
+      <c r="C471" s="8">
         <v>336659.51</v>
       </c>
     </row>
@@ -10161,7 +10163,7 @@
       <c r="B472" s="4" t="s">
         <v>938</v>
       </c>
-      <c r="C472" s="7">
+      <c r="C472" s="8">
         <v>231000.16500000001</v>
       </c>
     </row>
@@ -10172,7 +10174,7 @@
       <c r="B473" s="4" t="s">
         <v>940</v>
       </c>
-      <c r="C473" s="7">
+      <c r="C473" s="8">
         <v>246566.74900000001</v>
       </c>
     </row>
@@ -10183,7 +10185,7 @@
       <c r="B474" s="4" t="s">
         <v>942</v>
       </c>
-      <c r="C474" s="7">
+      <c r="C474" s="8">
         <v>246566.74900000001</v>
       </c>
     </row>
@@ -10194,7 +10196,7 @@
       <c r="B475" s="4" t="s">
         <v>944</v>
       </c>
-      <c r="C475" s="7">
+      <c r="C475" s="8">
         <v>336659.53200000001</v>
       </c>
     </row>
@@ -10205,7 +10207,7 @@
       <c r="B476" s="4" t="s">
         <v>946</v>
       </c>
-      <c r="C476" s="7">
+      <c r="C476" s="8">
         <v>231000.16500000001</v>
       </c>
     </row>
@@ -10216,7 +10218,7 @@
       <c r="B477" s="4" t="s">
         <v>948</v>
       </c>
-      <c r="C477" s="7">
+      <c r="C477" s="8">
         <v>414438.35400000005</v>
       </c>
     </row>
@@ -10227,7 +10229,7 @@
       <c r="B478" s="4" t="s">
         <v>950</v>
       </c>
-      <c r="C478" s="7">
+      <c r="C478" s="8">
         <v>386245.92599999998</v>
       </c>
     </row>
@@ -10238,7 +10240,7 @@
       <c r="B479" s="4" t="s">
         <v>952</v>
       </c>
-      <c r="C479" s="7">
+      <c r="C479" s="8">
         <v>389294.04800000001</v>
       </c>
     </row>
@@ -10249,7 +10251,7 @@
       <c r="B480" s="4" t="s">
         <v>954</v>
       </c>
-      <c r="C480" s="7">
+      <c r="C480" s="8">
         <v>240580.78</v>
       </c>
     </row>
@@ -10260,7 +10262,7 @@
       <c r="B481" s="4" t="s">
         <v>956</v>
       </c>
-      <c r="C481" s="7">
+      <c r="C481" s="8">
         <v>222802.20600000001</v>
       </c>
     </row>
@@ -10271,7 +10273,7 @@
       <c r="B482" s="4" t="s">
         <v>958</v>
       </c>
-      <c r="C482" s="7">
+      <c r="C482" s="8">
         <v>222802.98700000002</v>
       </c>
     </row>
@@ -10282,7 +10284,7 @@
       <c r="B483" s="4" t="s">
         <v>960</v>
       </c>
-      <c r="C483" s="7">
+      <c r="C483" s="8">
         <v>240580.307</v>
       </c>
     </row>
@@ -10293,7 +10295,7 @@
       <c r="B484" s="4" t="s">
         <v>962</v>
       </c>
-      <c r="C484" s="7">
+      <c r="C484" s="8">
         <v>222802.20600000001</v>
       </c>
     </row>
@@ -10304,7 +10306,7 @@
       <c r="B485" s="4" t="s">
         <v>964</v>
       </c>
-      <c r="C485" s="7">
+      <c r="C485" s="8">
         <v>222802.98700000002</v>
       </c>
     </row>
@@ -10315,7 +10317,7 @@
       <c r="B486" s="4" t="s">
         <v>966</v>
       </c>
-      <c r="C486" s="7">
+      <c r="C486" s="8">
         <v>224692.47900000002</v>
       </c>
     </row>
@@ -10326,7 +10328,7 @@
       <c r="B487" s="4" t="s">
         <v>968</v>
       </c>
-      <c r="C487" s="7">
+      <c r="C487" s="8">
         <v>207418.43100000001</v>
       </c>
     </row>
@@ -10337,7 +10339,7 @@
       <c r="B488" s="4" t="s">
         <v>970</v>
       </c>
-      <c r="C488" s="7">
+      <c r="C488" s="8">
         <v>224692.47900000002</v>
       </c>
     </row>
@@ -10348,7 +10350,7 @@
       <c r="B489" s="4" t="s">
         <v>972</v>
       </c>
-      <c r="C489" s="7">
+      <c r="C489" s="8">
         <v>207418.43100000001</v>
       </c>
     </row>
@@ -10359,7 +10361,7 @@
       <c r="B490" s="4" t="s">
         <v>974</v>
       </c>
-      <c r="C490" s="7">
+      <c r="C490" s="8">
         <v>68986.137000000002</v>
       </c>
     </row>
@@ -10370,18 +10372,18 @@
       <c r="B491" s="4" t="s">
         <v>976</v>
       </c>
-      <c r="C491" s="7">
+      <c r="C491" s="8">
         <v>68986.137000000002</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A492" s="6" t="s">
+      <c r="A492" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="B492" s="6" t="s">
+      <c r="B492" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="C492" s="7"/>
+      <c r="C492" s="8"/>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" s="4" t="s">
@@ -10390,7 +10392,7 @@
       <c r="B493" s="4" t="s">
         <v>980</v>
       </c>
-      <c r="C493" s="7">
+      <c r="C493" s="8">
         <v>601217.88100000005</v>
       </c>
     </row>
@@ -10401,7 +10403,7 @@
       <c r="B494" s="4" t="s">
         <v>982</v>
       </c>
-      <c r="C494" s="7">
+      <c r="C494" s="8">
         <v>495549.34000000008</v>
       </c>
     </row>
@@ -10412,7 +10414,7 @@
       <c r="B495" s="4" t="s">
         <v>984</v>
       </c>
-      <c r="C495" s="7">
+      <c r="C495" s="8">
         <v>564754.25600000005</v>
       </c>
     </row>
@@ -10423,7 +10425,7 @@
       <c r="B496" s="4" t="s">
         <v>986</v>
       </c>
-      <c r="C496" s="7">
+      <c r="C496" s="8">
         <v>372687.55700000003</v>
       </c>
     </row>
@@ -10434,7 +10436,7 @@
       <c r="B497" s="4" t="s">
         <v>988</v>
       </c>
-      <c r="C497" s="7">
+      <c r="C497" s="8">
         <v>352344.75099999999</v>
       </c>
     </row>
@@ -10445,7 +10447,7 @@
       <c r="B498" s="4" t="s">
         <v>990</v>
       </c>
-      <c r="C498" s="7">
+      <c r="C498" s="8">
         <v>352349.44800000003</v>
       </c>
     </row>
@@ -10456,7 +10458,7 @@
       <c r="B499" s="4" t="s">
         <v>992</v>
       </c>
-      <c r="C499" s="7">
+      <c r="C499" s="8">
         <v>372687.55700000003</v>
       </c>
     </row>
@@ -10467,7 +10469,7 @@
       <c r="B500" s="4" t="s">
         <v>994</v>
       </c>
-      <c r="C500" s="7">
+      <c r="C500" s="8">
         <v>352344.75099999999</v>
       </c>
     </row>
@@ -10478,7 +10480,7 @@
       <c r="B501" s="4" t="s">
         <v>996</v>
       </c>
-      <c r="C501" s="7">
+      <c r="C501" s="8">
         <v>352344.75099999999</v>
       </c>
     </row>
@@ -10489,7 +10491,7 @@
       <c r="B502" s="4" t="s">
         <v>998</v>
       </c>
-      <c r="C502" s="7">
+      <c r="C502" s="8">
         <v>342195.755</v>
       </c>
     </row>
@@ -10500,7 +10502,7 @@
       <c r="B503" s="4" t="s">
         <v>1000</v>
       </c>
-      <c r="C503" s="7">
+      <c r="C503" s="8">
         <v>342195.755</v>
       </c>
     </row>
@@ -10511,7 +10513,7 @@
       <c r="B504" s="4" t="s">
         <v>1002</v>
       </c>
-      <c r="C504" s="7">
+      <c r="C504" s="8">
         <v>342195.755</v>
       </c>
     </row>
@@ -10522,7 +10524,7 @@
       <c r="B505" s="4" t="s">
         <v>1004</v>
       </c>
-      <c r="C505" s="7">
+      <c r="C505" s="8">
         <v>342195.755</v>
       </c>
     </row>
@@ -10533,7 +10535,7 @@
       <c r="B506" s="4" t="s">
         <v>1006</v>
       </c>
-      <c r="C506" s="7">
+      <c r="C506" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10544,7 +10546,7 @@
       <c r="B507" s="4" t="s">
         <v>1008</v>
       </c>
-      <c r="C507" s="7">
+      <c r="C507" s="8">
         <v>291669.02600000001</v>
       </c>
     </row>
@@ -10555,7 +10557,7 @@
       <c r="B508" s="4" t="s">
         <v>1010</v>
       </c>
-      <c r="C508" s="7">
+      <c r="C508" s="8">
         <v>232681.60300000003</v>
       </c>
     </row>
@@ -10566,7 +10568,7 @@
       <c r="B509" s="4" t="s">
         <v>1012</v>
       </c>
-      <c r="C509" s="7">
+      <c r="C509" s="8">
         <v>291669.02600000001</v>
       </c>
     </row>
@@ -10577,7 +10579,7 @@
       <c r="B510" s="4" t="s">
         <v>1014</v>
       </c>
-      <c r="C510" s="7">
+      <c r="C510" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10588,7 +10590,7 @@
       <c r="B511" s="4" t="s">
         <v>1016</v>
       </c>
-      <c r="C511" s="7">
+      <c r="C511" s="8">
         <v>239834.01200000005</v>
       </c>
     </row>
@@ -10599,7 +10601,7 @@
       <c r="B512" s="4" t="s">
         <v>1018</v>
       </c>
-      <c r="C512" s="7">
+      <c r="C512" s="8">
         <v>223808.772</v>
       </c>
     </row>
@@ -10610,7 +10612,7 @@
       <c r="B513" s="4" t="s">
         <v>1020</v>
       </c>
-      <c r="C513" s="7">
+      <c r="C513" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10621,7 +10623,7 @@
       <c r="B514" s="4" t="s">
         <v>1022</v>
       </c>
-      <c r="C514" s="7">
+      <c r="C514" s="8">
         <v>239834.01200000005</v>
       </c>
     </row>
@@ -10632,7 +10634,7 @@
       <c r="B515" s="4" t="s">
         <v>1024</v>
       </c>
-      <c r="C515" s="7">
+      <c r="C515" s="8">
         <v>233531.30900000001</v>
       </c>
     </row>
@@ -10643,7 +10645,7 @@
       <c r="B516" s="4" t="s">
         <v>1026</v>
       </c>
-      <c r="C516" s="7">
+      <c r="C516" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10654,7 +10656,7 @@
       <c r="B517" s="4" t="s">
         <v>1028</v>
       </c>
-      <c r="C517" s="7">
+      <c r="C517" s="8">
         <v>264197.08700000006</v>
       </c>
     </row>
@@ -10665,7 +10667,7 @@
       <c r="B518" s="4" t="s">
         <v>1030</v>
       </c>
-      <c r="C518" s="7">
+      <c r="C518" s="8">
         <v>260532.19500000004</v>
       </c>
     </row>
@@ -10676,7 +10678,7 @@
       <c r="B519" s="4" t="s">
         <v>1032</v>
       </c>
-      <c r="C519" s="7">
+      <c r="C519" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10687,7 +10689,7 @@
       <c r="B520" s="4" t="s">
         <v>1034</v>
       </c>
-      <c r="C520" s="7">
+      <c r="C520" s="8">
         <v>264197.08700000006</v>
       </c>
     </row>
@@ -10698,7 +10700,7 @@
       <c r="B521" s="4" t="s">
         <v>1036</v>
       </c>
-      <c r="C521" s="7">
+      <c r="C521" s="8">
         <v>260532.19500000004</v>
       </c>
     </row>
@@ -10709,7 +10711,7 @@
       <c r="B522" s="4" t="s">
         <v>1038</v>
       </c>
-      <c r="C522" s="7">
+      <c r="C522" s="8">
         <v>310956.85500000004</v>
       </c>
     </row>
@@ -10720,7 +10722,7 @@
       <c r="B523" s="4" t="s">
         <v>1040</v>
       </c>
-      <c r="C523" s="7">
+      <c r="C523" s="8">
         <v>310956.85500000004</v>
       </c>
     </row>
@@ -10731,7 +10733,7 @@
       <c r="B524" s="4" t="s">
         <v>1042</v>
       </c>
-      <c r="C524" s="7">
+      <c r="C524" s="8">
         <v>341494.74700000003</v>
       </c>
     </row>
@@ -10742,18 +10744,18 @@
       <c r="B525" s="4" t="s">
         <v>1044</v>
       </c>
-      <c r="C525" s="7">
+      <c r="C525" s="8">
         <v>341494.74700000003</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A526" s="6" t="s">
+      <c r="A526" s="5" t="s">
         <v>1045</v>
       </c>
-      <c r="B526" s="6" t="s">
+      <c r="B526" s="5" t="s">
         <v>1046</v>
       </c>
-      <c r="C526" s="7"/>
+      <c r="C526" s="8"/>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" s="4" t="s">
@@ -10762,7 +10764,7 @@
       <c r="B527" s="4" t="s">
         <v>1048</v>
       </c>
-      <c r="C527" s="7">
+      <c r="C527" s="8">
         <v>263364.24400000001</v>
       </c>
     </row>
@@ -10773,7 +10775,7 @@
       <c r="B528" s="4" t="s">
         <v>1050</v>
       </c>
-      <c r="C528" s="7">
+      <c r="C528" s="8">
         <v>251620.27000000002</v>
       </c>
     </row>
@@ -10784,7 +10786,7 @@
       <c r="B529" s="4" t="s">
         <v>1052</v>
       </c>
-      <c r="C529" s="7">
+      <c r="C529" s="8">
         <v>263364.24400000001</v>
       </c>
     </row>
@@ -10795,7 +10797,7 @@
       <c r="B530" s="4" t="s">
         <v>1054</v>
       </c>
-      <c r="C530" s="7">
+      <c r="C530" s="8">
         <v>251620.27000000002</v>
       </c>
     </row>
@@ -10806,7 +10808,7 @@
       <c r="B531" s="4" t="s">
         <v>1056</v>
       </c>
-      <c r="C531" s="7">
+      <c r="C531" s="8">
         <v>252519.58600000004</v>
       </c>
     </row>
@@ -10817,7 +10819,7 @@
       <c r="B532" s="4" t="s">
         <v>1058</v>
       </c>
-      <c r="C532" s="7">
+      <c r="C532" s="8">
         <v>241539.94700000001</v>
       </c>
     </row>
@@ -10828,7 +10830,7 @@
       <c r="B533" s="4" t="s">
         <v>1060</v>
       </c>
-      <c r="C533" s="7">
+      <c r="C533" s="8">
         <v>252519.25600000002</v>
       </c>
     </row>
@@ -10839,7 +10841,7 @@
       <c r="B534" s="4" t="s">
         <v>1062</v>
       </c>
-      <c r="C534" s="7">
+      <c r="C534" s="8">
         <v>241539.94700000001</v>
       </c>
     </row>
@@ -10850,7 +10852,7 @@
       <c r="B535" s="4" t="s">
         <v>1064</v>
       </c>
-      <c r="C535" s="7">
+      <c r="C535" s="8">
         <v>666487.27200000011</v>
       </c>
     </row>
@@ -10861,7 +10863,7 @@
       <c r="B536" s="4" t="s">
         <v>1066</v>
       </c>
-      <c r="C536" s="7">
+      <c r="C536" s="8">
         <v>486210.89000000007</v>
       </c>
     </row>
@@ -10872,7 +10874,7 @@
       <c r="B537" s="4" t="s">
         <v>1068</v>
       </c>
-      <c r="C537" s="7">
+      <c r="C537" s="8">
         <v>574751.13300000003</v>
       </c>
     </row>
@@ -10883,7 +10885,7 @@
       <c r="B538" s="4" t="s">
         <v>1070</v>
       </c>
-      <c r="C538" s="7">
+      <c r="C538" s="8">
         <v>394346.10600000003</v>
       </c>
     </row>
@@ -10894,7 +10896,7 @@
       <c r="B539" s="4" t="s">
         <v>1072</v>
       </c>
-      <c r="C539" s="7">
+      <c r="C539" s="8">
         <v>399545.212</v>
       </c>
     </row>
@@ -10905,7 +10907,7 @@
       <c r="B540" s="4" t="s">
         <v>1074</v>
       </c>
-      <c r="C540" s="7">
+      <c r="C540" s="8">
         <v>257151.52100000001</v>
       </c>
     </row>
@@ -10916,7 +10918,7 @@
       <c r="B541" s="4" t="s">
         <v>1076</v>
       </c>
-      <c r="C541" s="7">
+      <c r="C541" s="8">
         <v>257301.09900000002</v>
       </c>
     </row>
@@ -10927,7 +10929,7 @@
       <c r="B542" s="4" t="s">
         <v>1078</v>
       </c>
-      <c r="C542" s="7">
+      <c r="C542" s="8">
         <v>257151.52100000001</v>
       </c>
     </row>
@@ -10938,7 +10940,7 @@
       <c r="B543" s="4" t="s">
         <v>1080</v>
       </c>
-      <c r="C543" s="7">
+      <c r="C543" s="8">
         <v>257301.09900000002</v>
       </c>
     </row>
@@ -10949,7 +10951,7 @@
       <c r="B544" s="4" t="s">
         <v>1082</v>
       </c>
-      <c r="C544" s="7">
+      <c r="C544" s="8">
         <v>186008.66900000002</v>
       </c>
     </row>
@@ -10960,7 +10962,7 @@
       <c r="B545" s="4" t="s">
         <v>1084</v>
       </c>
-      <c r="C545" s="7">
+      <c r="C545" s="8">
         <v>210797.37800000003</v>
       </c>
     </row>
@@ -10971,7 +10973,7 @@
       <c r="B546" s="4" t="s">
         <v>1086</v>
       </c>
-      <c r="C546" s="7">
+      <c r="C546" s="8">
         <v>186008.66900000002</v>
       </c>
     </row>
@@ -10982,7 +10984,7 @@
       <c r="B547" s="4" t="s">
         <v>1088</v>
       </c>
-      <c r="C547" s="7">
+      <c r="C547" s="8">
         <v>210785.96000000002</v>
       </c>
     </row>
@@ -10993,7 +10995,7 @@
       <c r="B548" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="C548" s="7">
+      <c r="C548" s="8">
         <v>358934.103</v>
       </c>
     </row>
@@ -11004,7 +11006,7 @@
       <c r="B549" s="4" t="s">
         <v>1092</v>
       </c>
-      <c r="C549" s="7">
+      <c r="C549" s="8">
         <v>273118.46100000001</v>
       </c>
     </row>
@@ -11015,7 +11017,7 @@
       <c r="B550" s="4" t="s">
         <v>1094</v>
       </c>
-      <c r="C550" s="7">
+      <c r="C550" s="8">
         <v>336679.84900000005</v>
       </c>
     </row>
@@ -11026,7 +11028,7 @@
       <c r="B551" s="4" t="s">
         <v>1096</v>
       </c>
-      <c r="C551" s="7">
+      <c r="C551" s="8">
         <v>226955.86100000003</v>
       </c>
     </row>
@@ -11037,7 +11039,7 @@
       <c r="B552" s="4" t="s">
         <v>1098</v>
       </c>
-      <c r="C552" s="7">
+      <c r="C552" s="8">
         <v>268502.47600000002</v>
       </c>
     </row>
@@ -11048,7 +11050,7 @@
       <c r="B553" s="4" t="s">
         <v>1100</v>
       </c>
-      <c r="C553" s="7">
+      <c r="C553" s="8">
         <v>217156.18100000001</v>
       </c>
     </row>
@@ -11059,7 +11061,7 @@
       <c r="B554" s="4" t="s">
         <v>1102</v>
       </c>
-      <c r="C554" s="7">
+      <c r="C554" s="8">
         <v>226955.86100000003</v>
       </c>
     </row>
@@ -11070,7 +11072,7 @@
       <c r="B555" s="4" t="s">
         <v>1104</v>
       </c>
-      <c r="C555" s="7">
+      <c r="C555" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11081,7 +11083,7 @@
       <c r="B556" s="4" t="s">
         <v>1106</v>
       </c>
-      <c r="C556" s="7">
+      <c r="C556" s="8">
         <v>253608.04700000002</v>
       </c>
     </row>
@@ -11092,7 +11094,7 @@
       <c r="B557" s="4" t="s">
         <v>1108</v>
       </c>
-      <c r="C557" s="7">
+      <c r="C557" s="8">
         <v>253608.04700000002</v>
       </c>
     </row>
@@ -11103,7 +11105,7 @@
       <c r="B558" s="4" t="s">
         <v>1110</v>
       </c>
-      <c r="C558" s="7">
+      <c r="C558" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11114,7 +11116,7 @@
       <c r="B559" s="4" t="s">
         <v>1112</v>
       </c>
-      <c r="C559" s="7">
+      <c r="C559" s="8">
         <v>253608.04700000002</v>
       </c>
     </row>
@@ -11125,7 +11127,7 @@
       <c r="B560" s="4" t="s">
         <v>1114</v>
       </c>
-      <c r="C560" s="7">
+      <c r="C560" s="8">
         <v>253608.04700000002</v>
       </c>
     </row>
@@ -11136,7 +11138,7 @@
       <c r="B561" s="4" t="s">
         <v>1116</v>
       </c>
-      <c r="C561" s="7">
+      <c r="C561" s="8">
         <v>240043.68300000002</v>
       </c>
     </row>
@@ -11147,7 +11149,7 @@
       <c r="B562" s="4" t="s">
         <v>1118</v>
       </c>
-      <c r="C562" s="7">
+      <c r="C562" s="8">
         <v>224889.11500000002</v>
       </c>
     </row>
@@ -11158,7 +11160,7 @@
       <c r="B563" s="4" t="s">
         <v>1120</v>
       </c>
-      <c r="C563" s="7">
+      <c r="C563" s="8">
         <v>132357.44500000001</v>
       </c>
     </row>
@@ -11169,7 +11171,7 @@
       <c r="B564" s="4" t="s">
         <v>1122</v>
       </c>
-      <c r="C564" s="7">
+      <c r="C564" s="8">
         <v>240043.68300000002</v>
       </c>
     </row>
@@ -11180,7 +11182,7 @@
       <c r="B565" s="4" t="s">
         <v>1124</v>
       </c>
-      <c r="C565" s="7">
+      <c r="C565" s="8">
         <v>224889.11500000002</v>
       </c>
     </row>
@@ -11191,7 +11193,7 @@
       <c r="B566" s="4" t="s">
         <v>1126</v>
       </c>
-      <c r="C566" s="7">
+      <c r="C566" s="8">
         <v>232600.88500000004</v>
       </c>
     </row>
@@ -11202,7 +11204,7 @@
       <c r="B567" s="4" t="s">
         <v>1128</v>
       </c>
-      <c r="C567" s="7">
+      <c r="C567" s="8">
         <v>232600.88500000004</v>
       </c>
     </row>
@@ -11213,7 +11215,7 @@
       <c r="B568" s="4" t="s">
         <v>1130</v>
       </c>
-      <c r="C568" s="7">
+      <c r="C568" s="8">
         <v>232600.88500000004</v>
       </c>
     </row>
@@ -11224,7 +11226,7 @@
       <c r="B569" s="4" t="s">
         <v>1132</v>
       </c>
-      <c r="C569" s="7">
+      <c r="C569" s="8">
         <v>232600.88500000004</v>
       </c>
     </row>
@@ -11235,7 +11237,7 @@
       <c r="B570" s="4" t="s">
         <v>1134</v>
       </c>
-      <c r="C570" s="7">
+      <c r="C570" s="8">
         <v>369156.64500000002</v>
       </c>
     </row>
@@ -11246,18 +11248,18 @@
       <c r="B571" s="4" t="s">
         <v>1136</v>
       </c>
-      <c r="C571" s="7">
+      <c r="C571" s="8">
         <v>369156.64500000002</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A572" s="6" t="s">
+      <c r="A572" s="5" t="s">
         <v>1137</v>
       </c>
-      <c r="B572" s="6" t="s">
+      <c r="B572" s="5" t="s">
         <v>1138</v>
       </c>
-      <c r="C572" s="7"/>
+      <c r="C572" s="8"/>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A573" s="4" t="s">
@@ -11266,7 +11268,7 @@
       <c r="B573" s="4" t="s">
         <v>1140</v>
       </c>
-      <c r="C573" s="7">
+      <c r="C573" s="8">
         <v>192351.18100000001</v>
       </c>
     </row>
@@ -11277,7 +11279,7 @@
       <c r="B574" s="4" t="s">
         <v>1142</v>
       </c>
-      <c r="C574" s="7">
+      <c r="C574" s="8">
         <v>238600.098</v>
       </c>
     </row>
@@ -11288,7 +11290,7 @@
       <c r="B575" s="4" t="s">
         <v>1144</v>
       </c>
-      <c r="C575" s="7">
+      <c r="C575" s="8">
         <v>238600.098</v>
       </c>
     </row>
@@ -11299,7 +11301,7 @@
       <c r="B576" s="4" t="s">
         <v>1146</v>
       </c>
-      <c r="C576" s="7">
+      <c r="C576" s="8">
         <v>214262.93900000001</v>
       </c>
     </row>
@@ -11310,7 +11312,7 @@
       <c r="B577" s="4" t="s">
         <v>1148</v>
       </c>
-      <c r="C577" s="7">
+      <c r="C577" s="8">
         <v>214262.93900000001</v>
       </c>
     </row>
@@ -11321,7 +11323,7 @@
       <c r="B578" s="4" t="s">
         <v>1150</v>
       </c>
-      <c r="C578" s="7">
+      <c r="C578" s="8">
         <v>214262.93900000001</v>
       </c>
     </row>
@@ -11332,7 +11334,7 @@
       <c r="B579" s="4" t="s">
         <v>1152</v>
       </c>
-      <c r="C579" s="7">
+      <c r="C579" s="8">
         <v>214262.93900000001</v>
       </c>
     </row>
@@ -11343,7 +11345,7 @@
       <c r="B580" s="4" t="s">
         <v>1154</v>
       </c>
-      <c r="C580" s="7">
+      <c r="C580" s="8">
         <v>177586.99200000003</v>
       </c>
     </row>
@@ -11354,7 +11356,7 @@
       <c r="B581" s="4" t="s">
         <v>1156</v>
       </c>
-      <c r="C581" s="7">
+      <c r="C581" s="8">
         <v>177586.99200000003</v>
       </c>
     </row>
@@ -11365,7 +11367,7 @@
       <c r="B582" s="4" t="s">
         <v>1158</v>
       </c>
-      <c r="C582" s="7">
+      <c r="C582" s="8">
         <v>177586.99200000003</v>
       </c>
     </row>
@@ -11376,7 +11378,7 @@
       <c r="B583" s="4" t="s">
         <v>1160</v>
       </c>
-      <c r="C583" s="7">
+      <c r="C583" s="8">
         <v>177586.99200000003</v>
       </c>
     </row>
@@ -11387,7 +11389,7 @@
       <c r="B584" s="4" t="s">
         <v>1162</v>
       </c>
-      <c r="C584" s="7">
+      <c r="C584" s="8">
         <v>226148.08700000003</v>
       </c>
     </row>
@@ -11398,7 +11400,7 @@
       <c r="B585" s="4" t="s">
         <v>1164</v>
       </c>
-      <c r="C585" s="7">
+      <c r="C585" s="8">
         <v>237229.31100000002</v>
       </c>
     </row>
@@ -11409,7 +11411,7 @@
       <c r="B586" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="C586" s="7">
+      <c r="C586" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11420,7 +11422,7 @@
       <c r="B587" s="4" t="s">
         <v>1168</v>
       </c>
-      <c r="C587" s="7">
+      <c r="C587" s="8">
         <v>237229.31100000002</v>
       </c>
     </row>
@@ -11431,7 +11433,7 @@
       <c r="B588" s="4" t="s">
         <v>1170</v>
       </c>
-      <c r="C588" s="7">
+      <c r="C588" s="8">
         <v>226148.08700000003</v>
       </c>
     </row>
@@ -11442,7 +11444,7 @@
       <c r="B589" s="4" t="s">
         <v>1172</v>
       </c>
-      <c r="C589" s="7">
+      <c r="C589" s="8">
         <v>237229.31100000002</v>
       </c>
     </row>
@@ -11453,7 +11455,7 @@
       <c r="B590" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="C590" s="7">
+      <c r="C590" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11464,7 +11466,7 @@
       <c r="B591" s="4" t="s">
         <v>1176</v>
       </c>
-      <c r="C591" s="7">
+      <c r="C591" s="8">
         <v>235900.50000000003</v>
       </c>
     </row>
@@ -11475,7 +11477,7 @@
       <c r="B592" s="4" t="s">
         <v>1178</v>
       </c>
-      <c r="C592" s="7">
+      <c r="C592" s="8">
         <v>225097.64200000002</v>
       </c>
     </row>
@@ -11486,7 +11488,7 @@
       <c r="B593" s="4" t="s">
         <v>1180</v>
       </c>
-      <c r="C593" s="7">
+      <c r="C593" s="8">
         <v>225097.64200000002</v>
       </c>
     </row>
@@ -11497,7 +11499,7 @@
       <c r="B594" s="4" t="s">
         <v>1182</v>
       </c>
-      <c r="C594" s="7">
+      <c r="C594" s="8">
         <v>295968.739</v>
       </c>
     </row>
@@ -11508,18 +11510,18 @@
       <c r="B595" s="4" t="s">
         <v>1184</v>
       </c>
-      <c r="C595" s="7">
+      <c r="C595" s="8">
         <v>295968.75</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A596" s="6" t="s">
+      <c r="A596" s="5" t="s">
         <v>1185</v>
       </c>
-      <c r="B596" s="6" t="s">
+      <c r="B596" s="5" t="s">
         <v>1186</v>
       </c>
-      <c r="C596" s="7"/>
+      <c r="C596" s="8"/>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597" s="4" t="s">
@@ -11528,7 +11530,7 @@
       <c r="B597" s="4" t="s">
         <v>1188</v>
       </c>
-      <c r="C597" s="7">
+      <c r="C597" s="8">
         <v>300603.56699999998</v>
       </c>
     </row>
@@ -11539,7 +11541,7 @@
       <c r="B598" s="4" t="s">
         <v>1190</v>
       </c>
-      <c r="C598" s="7">
+      <c r="C598" s="8">
         <v>300603.56699999998</v>
       </c>
     </row>
@@ -11550,7 +11552,7 @@
       <c r="B599" s="4" t="s">
         <v>1192</v>
       </c>
-      <c r="C599" s="7">
+      <c r="C599" s="8">
         <v>300603.56699999998</v>
       </c>
     </row>
@@ -11561,7 +11563,7 @@
       <c r="B600" s="4" t="s">
         <v>1194</v>
       </c>
-      <c r="C600" s="7">
+      <c r="C600" s="8">
         <v>302518.52400000003</v>
       </c>
     </row>
@@ -11572,7 +11574,7 @@
       <c r="B601" s="4" t="s">
         <v>1196</v>
       </c>
-      <c r="C601" s="7">
+      <c r="C601" s="8">
         <v>243105.45600000001</v>
       </c>
     </row>
@@ -11583,7 +11585,7 @@
       <c r="B602" s="4" t="s">
         <v>1198</v>
       </c>
-      <c r="C602" s="7">
+      <c r="C602" s="8">
         <v>243105.45600000001</v>
       </c>
     </row>
@@ -11594,7 +11596,7 @@
       <c r="B603" s="4" t="s">
         <v>1200</v>
       </c>
-      <c r="C603" s="7">
+      <c r="C603" s="8">
         <v>243105.45600000001</v>
       </c>
     </row>
@@ -11605,7 +11607,7 @@
       <c r="B604" s="4" t="s">
         <v>1202</v>
       </c>
-      <c r="C604" s="7">
+      <c r="C604" s="8">
         <v>243105.45600000001</v>
       </c>
     </row>
@@ -11616,7 +11618,7 @@
       <c r="B605" s="4" t="s">
         <v>1204</v>
       </c>
-      <c r="C605" s="7">
+      <c r="C605" s="8">
         <v>243105.45600000001</v>
       </c>
     </row>
@@ -11627,7 +11629,7 @@
       <c r="B606" s="4" t="s">
         <v>1206</v>
       </c>
-      <c r="C606" s="7">
+      <c r="C606" s="8">
         <v>243105.45600000001</v>
       </c>
     </row>
@@ -11638,7 +11640,7 @@
       <c r="B607" s="4" t="s">
         <v>1208</v>
       </c>
-      <c r="C607" s="7">
+      <c r="C607" s="8">
         <v>316034.66399999999</v>
       </c>
     </row>
@@ -11649,18 +11651,18 @@
       <c r="B608" s="4" t="s">
         <v>1210</v>
       </c>
-      <c r="C608" s="7">
+      <c r="C608" s="8">
         <v>316034.66399999999</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A609" s="6" t="s">
+      <c r="A609" s="5" t="s">
         <v>1211</v>
       </c>
-      <c r="B609" s="6" t="s">
+      <c r="B609" s="5" t="s">
         <v>1212</v>
       </c>
-      <c r="C609" s="7"/>
+      <c r="C609" s="8"/>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A610" s="4" t="s">
@@ -11669,7 +11671,7 @@
       <c r="B610" s="4" t="s">
         <v>1214</v>
       </c>
-      <c r="C610" s="7">
+      <c r="C610" s="8">
         <v>240975.46000000002</v>
       </c>
     </row>
@@ -11680,7 +11682,7 @@
       <c r="B611" s="4" t="s">
         <v>1216</v>
       </c>
-      <c r="C611" s="7">
+      <c r="C611" s="8">
         <v>228248.99900000001</v>
       </c>
     </row>
@@ -11691,7 +11693,7 @@
       <c r="B612" s="4" t="s">
         <v>1218</v>
       </c>
-      <c r="C612" s="7">
+      <c r="C612" s="8">
         <v>240975.46000000002</v>
       </c>
     </row>
@@ -11702,7 +11704,7 @@
       <c r="B613" s="4" t="s">
         <v>1220</v>
       </c>
-      <c r="C613" s="7">
+      <c r="C613" s="8">
         <v>253878.77900000004</v>
       </c>
     </row>
@@ -11713,7 +11715,7 @@
       <c r="B614" s="4" t="s">
         <v>1222</v>
       </c>
-      <c r="C614" s="7">
+      <c r="C614" s="8">
         <v>242782.80400000003</v>
       </c>
     </row>
@@ -11724,18 +11726,18 @@
       <c r="B615" s="4" t="s">
         <v>1224</v>
       </c>
-      <c r="C615" s="7">
+      <c r="C615" s="8">
         <v>253878.77900000004</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A616" s="6" t="s">
+      <c r="A616" s="5" t="s">
         <v>1225</v>
       </c>
-      <c r="B616" s="6" t="s">
+      <c r="B616" s="5" t="s">
         <v>1226</v>
       </c>
-      <c r="C616" s="7"/>
+      <c r="C616" s="8"/>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617" s="4" t="s">
@@ -11744,7 +11746,7 @@
       <c r="B617" s="4" t="s">
         <v>1228</v>
       </c>
-      <c r="C617" s="7">
+      <c r="C617" s="8">
         <v>241004.522</v>
       </c>
     </row>
@@ -11755,7 +11757,7 @@
       <c r="B618" s="4" t="s">
         <v>1230</v>
       </c>
-      <c r="C618" s="7">
+      <c r="C618" s="8">
         <v>214417.02700000003</v>
       </c>
     </row>
@@ -11766,7 +11768,7 @@
       <c r="B619" s="4" t="s">
         <v>1232</v>
       </c>
-      <c r="C619" s="7">
+      <c r="C619" s="8">
         <v>241004.522</v>
       </c>
     </row>
@@ -11777,7 +11779,7 @@
       <c r="B620" s="4" t="s">
         <v>1234</v>
       </c>
-      <c r="C620" s="7">
+      <c r="C620" s="8">
         <v>214417.02700000003</v>
       </c>
     </row>
@@ -11788,7 +11790,7 @@
       <c r="B621" s="4" t="s">
         <v>1236</v>
       </c>
-      <c r="C621" s="7">
+      <c r="C621" s="8">
         <v>196285.122</v>
       </c>
     </row>
@@ -11799,7 +11801,7 @@
       <c r="B622" s="4" t="s">
         <v>1238</v>
       </c>
-      <c r="C622" s="7">
+      <c r="C622" s="8">
         <v>333418.26100000006</v>
       </c>
     </row>
@@ -11810,7 +11812,7 @@
       <c r="B623" s="4" t="s">
         <v>1240</v>
       </c>
-      <c r="C623" s="7">
+      <c r="C623" s="8">
         <v>196284.913</v>
       </c>
     </row>
@@ -11821,18 +11823,18 @@
       <c r="B624" s="4" t="s">
         <v>1242</v>
       </c>
-      <c r="C624" s="7">
+      <c r="C624" s="8">
         <v>333418.26100000006</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A625" s="6" t="s">
+      <c r="A625" s="5" t="s">
         <v>1243</v>
       </c>
-      <c r="B625" s="6" t="s">
+      <c r="B625" s="5" t="s">
         <v>1244</v>
       </c>
-      <c r="C625" s="7"/>
+      <c r="C625" s="8"/>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626" s="4" t="s">
@@ -11841,7 +11843,7 @@
       <c r="B626" s="4" t="s">
         <v>1246</v>
       </c>
-      <c r="C626" s="7">
+      <c r="C626" s="8">
         <v>169648.58900000001</v>
       </c>
     </row>
@@ -11852,7 +11854,7 @@
       <c r="B627" s="4" t="s">
         <v>1248</v>
       </c>
-      <c r="C627" s="7">
+      <c r="C627" s="8">
         <v>126130.48800000001</v>
       </c>
     </row>
@@ -11863,7 +11865,7 @@
       <c r="B628" s="4" t="s">
         <v>1250</v>
       </c>
-      <c r="C628" s="7">
+      <c r="C628" s="8">
         <v>169648.58900000001</v>
       </c>
     </row>
@@ -11874,7 +11876,7 @@
       <c r="B629" s="4" t="s">
         <v>1252</v>
       </c>
-      <c r="C629" s="7">
+      <c r="C629" s="8">
         <v>126130.48800000001</v>
       </c>
     </row>
@@ -11885,7 +11887,7 @@
       <c r="B630" s="4" t="s">
         <v>1254</v>
       </c>
-      <c r="C630" s="7">
+      <c r="C630" s="8">
         <v>190882.76900000003</v>
       </c>
     </row>
@@ -11896,7 +11898,7 @@
       <c r="B631" s="4" t="s">
         <v>1256</v>
       </c>
-      <c r="C631" s="7">
+      <c r="C631" s="8">
         <v>220242.27500000002</v>
       </c>
     </row>
@@ -11907,7 +11909,7 @@
       <c r="B632" s="4" t="s">
         <v>1258</v>
       </c>
-      <c r="C632" s="7">
+      <c r="C632" s="8">
         <v>190882.76900000003</v>
       </c>
     </row>
@@ -11918,18 +11920,18 @@
       <c r="B633" s="4" t="s">
         <v>1260</v>
       </c>
-      <c r="C633" s="7">
+      <c r="C633" s="8">
         <v>220242.27500000002</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A634" s="6" t="s">
+      <c r="A634" s="5" t="s">
         <v>1261</v>
       </c>
-      <c r="B634" s="6" t="s">
+      <c r="B634" s="5" t="s">
         <v>1262</v>
       </c>
-      <c r="C634" s="7"/>
+      <c r="C634" s="8"/>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A635" s="4" t="s">
@@ -11938,7 +11940,7 @@
       <c r="B635" s="4" t="s">
         <v>1264</v>
       </c>
-      <c r="C635" s="7">
+      <c r="C635" s="8">
         <v>127555.31800000001</v>
       </c>
     </row>
@@ -11949,7 +11951,7 @@
       <c r="B636" s="4" t="s">
         <v>1266</v>
       </c>
-      <c r="C636" s="7">
+      <c r="C636" s="8">
         <v>94349.409000000014</v>
       </c>
     </row>
@@ -11960,7 +11962,7 @@
       <c r="B637" s="4" t="s">
         <v>1268</v>
       </c>
-      <c r="C637" s="7">
+      <c r="C637" s="8">
         <v>127555.31800000001</v>
       </c>
     </row>
@@ -11971,18 +11973,18 @@
       <c r="B638" s="4" t="s">
         <v>1270</v>
       </c>
-      <c r="C638" s="7">
+      <c r="C638" s="8">
         <v>94349.409000000014</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A639" s="6" t="s">
+      <c r="A639" s="5" t="s">
         <v>1271</v>
       </c>
-      <c r="B639" s="6" t="s">
+      <c r="B639" s="5" t="s">
         <v>1272</v>
       </c>
-      <c r="C639" s="7"/>
+      <c r="C639" s="8"/>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640" s="4" t="s">
@@ -11991,18 +11993,18 @@
       <c r="B640" s="4" t="s">
         <v>1274</v>
       </c>
-      <c r="C640" s="7">
+      <c r="C640" s="8">
         <v>470532.85400000005</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A641" s="6" t="s">
+      <c r="A641" s="5" t="s">
         <v>1275</v>
       </c>
-      <c r="B641" s="6" t="s">
+      <c r="B641" s="5" t="s">
         <v>1276</v>
       </c>
-      <c r="C641" s="7"/>
+      <c r="C641" s="8"/>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A642" s="4" t="s">
@@ -12011,7 +12013,7 @@
       <c r="B642" s="4" t="s">
         <v>1278</v>
       </c>
-      <c r="C642" s="7">
+      <c r="C642" s="8">
         <v>223412.70600000001</v>
       </c>
     </row>
@@ -12022,7 +12024,7 @@
       <c r="B643" s="4" t="s">
         <v>1280</v>
       </c>
-      <c r="C643" s="7">
+      <c r="C643" s="8">
         <v>223412.70600000001</v>
       </c>
     </row>
@@ -12033,7 +12035,7 @@
       <c r="B644" s="4" t="s">
         <v>1282</v>
       </c>
-      <c r="C644" s="7">
+      <c r="C644" s="8">
         <v>223412.70600000001</v>
       </c>
     </row>
@@ -12044,18 +12046,18 @@
       <c r="B645" s="4" t="s">
         <v>1284</v>
       </c>
-      <c r="C645" s="7">
+      <c r="C645" s="8">
         <v>223412.70600000001</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A646" s="6" t="s">
+      <c r="A646" s="5" t="s">
         <v>1285</v>
       </c>
-      <c r="B646" s="6" t="s">
+      <c r="B646" s="5" t="s">
         <v>1286</v>
       </c>
-      <c r="C646" s="7"/>
+      <c r="C646" s="8"/>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647" s="4" t="s">
@@ -12064,7 +12066,7 @@
       <c r="B647" s="4" t="s">
         <v>1288</v>
       </c>
-      <c r="C647" s="7">
+      <c r="C647" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12075,7 +12077,7 @@
       <c r="B648" s="4" t="s">
         <v>1290</v>
       </c>
-      <c r="C648" s="7">
+      <c r="C648" s="8">
         <v>253879.23</v>
       </c>
     </row>
@@ -12086,7 +12088,7 @@
       <c r="B649" s="4" t="s">
         <v>1292</v>
       </c>
-      <c r="C649" s="7">
+      <c r="C649" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12097,7 +12099,7 @@
       <c r="B650" s="4" t="s">
         <v>1294</v>
       </c>
-      <c r="C650" s="7">
+      <c r="C650" s="8">
         <v>220139.24900000001</v>
       </c>
     </row>
@@ -12108,7 +12110,7 @@
       <c r="B651" s="4" t="s">
         <v>1296</v>
       </c>
-      <c r="C651" s="7">
+      <c r="C651" s="8">
         <v>255728.48400000003</v>
       </c>
     </row>
@@ -12119,18 +12121,18 @@
       <c r="B652" s="4" t="s">
         <v>1298</v>
       </c>
-      <c r="C652" s="7">
+      <c r="C652" s="8">
         <v>255728.48400000003</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A653" s="6" t="s">
+      <c r="A653" s="5" t="s">
         <v>1299</v>
       </c>
-      <c r="B653" s="6" t="s">
+      <c r="B653" s="5" t="s">
         <v>1300</v>
       </c>
-      <c r="C653" s="7"/>
+      <c r="C653" s="8"/>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A654" s="4" t="s">
@@ -12139,7 +12141,7 @@
       <c r="B654" s="4" t="s">
         <v>1302</v>
       </c>
-      <c r="C654" s="7">
+      <c r="C654" s="8">
         <v>237403.28700000004</v>
       </c>
     </row>
@@ -12150,7 +12152,7 @@
       <c r="B655" s="4" t="s">
         <v>1304</v>
       </c>
-      <c r="C655" s="7">
+      <c r="C655" s="8">
         <v>340009.95600000006</v>
       </c>
     </row>
@@ -12161,7 +12163,7 @@
       <c r="B656" s="4" t="s">
         <v>1306</v>
       </c>
-      <c r="C656" s="7">
+      <c r="C656" s="8">
         <v>344482.38</v>
       </c>
     </row>
@@ -12172,7 +12174,7 @@
       <c r="B657" s="4" t="s">
         <v>1308</v>
       </c>
-      <c r="C657" s="7">
+      <c r="C657" s="8">
         <v>340009.95600000006</v>
       </c>
     </row>
@@ -12183,7 +12185,7 @@
       <c r="B658" s="4" t="s">
         <v>1310</v>
       </c>
-      <c r="C658" s="7">
+      <c r="C658" s="8">
         <v>344482.38</v>
       </c>
     </row>
@@ -12194,7 +12196,7 @@
       <c r="B659" s="4" t="s">
         <v>1312</v>
       </c>
-      <c r="C659" s="7">
+      <c r="C659" s="8">
         <v>237455.51500000001</v>
       </c>
     </row>
@@ -12205,7 +12207,7 @@
       <c r="B660" s="4" t="s">
         <v>1314</v>
       </c>
-      <c r="C660" s="7">
+      <c r="C660" s="8">
         <v>318467.875</v>
       </c>
     </row>
@@ -12216,18 +12218,18 @@
       <c r="B661" s="4" t="s">
         <v>1316</v>
       </c>
-      <c r="C661" s="7">
+      <c r="C661" s="8">
         <v>318467.875</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A662" s="6" t="s">
+      <c r="A662" s="5" t="s">
         <v>1317</v>
       </c>
-      <c r="B662" s="6" t="s">
+      <c r="B662" s="5" t="s">
         <v>1318</v>
       </c>
-      <c r="C662" s="7"/>
+      <c r="C662" s="8"/>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A663" s="4" t="s">
@@ -12236,7 +12238,7 @@
       <c r="B663" s="4" t="s">
         <v>1320</v>
       </c>
-      <c r="C663" s="7">
+      <c r="C663" s="8">
         <v>234919.38800000001</v>
       </c>
     </row>
@@ -12247,7 +12249,7 @@
       <c r="B664" s="4" t="s">
         <v>1322</v>
       </c>
-      <c r="C664" s="7">
+      <c r="C664" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12258,7 +12260,7 @@
       <c r="B665" s="4" t="s">
         <v>1324</v>
       </c>
-      <c r="C665" s="7">
+      <c r="C665" s="8">
         <v>234919.38800000001</v>
       </c>
     </row>
@@ -12269,18 +12271,18 @@
       <c r="B666" s="4" t="s">
         <v>1326</v>
       </c>
-      <c r="C666" s="7">
+      <c r="C666" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A667" s="6" t="s">
+      <c r="A667" s="5" t="s">
         <v>1327</v>
       </c>
-      <c r="B667" s="6" t="s">
+      <c r="B667" s="5" t="s">
         <v>1328</v>
       </c>
-      <c r="C667" s="7"/>
+      <c r="C667" s="8"/>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A668" s="4" t="s">
@@ -12289,7 +12291,7 @@
       <c r="B668" s="4" t="s">
         <v>1330</v>
       </c>
-      <c r="C668" s="7">
+      <c r="C668" s="8">
         <v>265266.28700000001</v>
       </c>
     </row>
@@ -12300,7 +12302,7 @@
       <c r="B669" s="4" t="s">
         <v>1332</v>
       </c>
-      <c r="C669" s="7">
+      <c r="C669" s="8">
         <v>265266.28700000001</v>
       </c>
     </row>
@@ -12311,7 +12313,7 @@
       <c r="B670" s="4" t="s">
         <v>1334</v>
       </c>
-      <c r="C670" s="7">
+      <c r="C670" s="8">
         <v>295239.87900000002</v>
       </c>
     </row>
@@ -12322,18 +12324,18 @@
       <c r="B671" s="4" t="s">
         <v>1336</v>
       </c>
-      <c r="C671" s="7">
+      <c r="C671" s="8">
         <v>295239.87900000002</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A672" s="6" t="s">
+      <c r="A672" s="5" t="s">
         <v>1337</v>
       </c>
-      <c r="B672" s="6" t="s">
+      <c r="B672" s="5" t="s">
         <v>1338</v>
       </c>
-      <c r="C672" s="7"/>
+      <c r="C672" s="8"/>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A673" s="4" t="s">
@@ -12342,7 +12344,7 @@
       <c r="B673" s="4" t="s">
         <v>1340</v>
       </c>
-      <c r="C673" s="7">
+      <c r="C673" s="8">
         <v>234698.37600000002</v>
       </c>
     </row>
@@ -12353,7 +12355,7 @@
       <c r="B674" s="4" t="s">
         <v>1342</v>
       </c>
-      <c r="C674" s="7">
+      <c r="C674" s="8">
         <v>210091.11200000002</v>
       </c>
     </row>
@@ -12364,7 +12366,7 @@
       <c r="B675" s="4" t="s">
         <v>1344</v>
       </c>
-      <c r="C675" s="7">
+      <c r="C675" s="8">
         <v>220138.87500000003</v>
       </c>
     </row>
@@ -12375,7 +12377,7 @@
       <c r="B676" s="4" t="s">
         <v>1346</v>
       </c>
-      <c r="C676" s="7">
+      <c r="C676" s="8">
         <v>234698.37600000002</v>
       </c>
     </row>
@@ -12386,7 +12388,7 @@
       <c r="B677" s="4" t="s">
         <v>1348</v>
       </c>
-      <c r="C677" s="7">
+      <c r="C677" s="8">
         <v>210091.11200000002</v>
       </c>
     </row>
@@ -12397,7 +12399,7 @@
       <c r="B678" s="4" t="s">
         <v>1350</v>
       </c>
-      <c r="C678" s="7">
+      <c r="C678" s="8">
         <v>220138.87500000003</v>
       </c>
     </row>
@@ -12408,7 +12410,7 @@
       <c r="B679" s="4" t="s">
         <v>1352</v>
       </c>
-      <c r="C679" s="7">
+      <c r="C679" s="8">
         <v>234698.37600000002</v>
       </c>
     </row>
@@ -12419,7 +12421,7 @@
       <c r="B680" s="4" t="s">
         <v>1354</v>
       </c>
-      <c r="C680" s="7">
+      <c r="C680" s="8">
         <v>210091.11200000002</v>
       </c>
     </row>
@@ -12430,7 +12432,7 @@
       <c r="B681" s="4" t="s">
         <v>1356</v>
       </c>
-      <c r="C681" s="7">
+      <c r="C681" s="8">
         <v>220138.87500000003</v>
       </c>
     </row>
@@ -12441,7 +12443,7 @@
       <c r="B682" s="4" t="s">
         <v>1358</v>
       </c>
-      <c r="C682" s="7">
+      <c r="C682" s="8">
         <v>234698.37600000002</v>
       </c>
     </row>
@@ -12452,7 +12454,7 @@
       <c r="B683" s="4" t="s">
         <v>1360</v>
       </c>
-      <c r="C683" s="7">
+      <c r="C683" s="8">
         <v>210091.11200000002</v>
       </c>
     </row>
@@ -12463,7 +12465,7 @@
       <c r="B684" s="4" t="s">
         <v>1362</v>
       </c>
-      <c r="C684" s="7">
+      <c r="C684" s="8">
         <v>220138.87500000003</v>
       </c>
     </row>
@@ -12474,7 +12476,7 @@
       <c r="B685" s="4" t="s">
         <v>1364</v>
       </c>
-      <c r="C685" s="7">
+      <c r="C685" s="8">
         <v>284555.326</v>
       </c>
     </row>
@@ -12485,18 +12487,18 @@
       <c r="B686" s="4" t="s">
         <v>1366</v>
       </c>
-      <c r="C686" s="7">
+      <c r="C686" s="8">
         <v>284555.326</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A687" s="6" t="s">
+      <c r="A687" s="5" t="s">
         <v>1367</v>
       </c>
-      <c r="B687" s="6" t="s">
+      <c r="B687" s="5" t="s">
         <v>1368</v>
       </c>
-      <c r="C687" s="7"/>
+      <c r="C687" s="8"/>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A688" s="4" t="s">
@@ -12505,7 +12507,7 @@
       <c r="B688" s="4" t="s">
         <v>1370</v>
       </c>
-      <c r="C688" s="7">
+      <c r="C688" s="8">
         <v>251073.90000000002</v>
       </c>
     </row>
@@ -12516,7 +12518,7 @@
       <c r="B689" s="4" t="s">
         <v>1372</v>
       </c>
-      <c r="C689" s="7">
+      <c r="C689" s="8">
         <v>251073.90000000002</v>
       </c>
     </row>
@@ -12527,7 +12529,7 @@
       <c r="B690" s="4" t="s">
         <v>1374</v>
       </c>
-      <c r="C690" s="7">
+      <c r="C690" s="8">
         <v>238603.45300000004</v>
       </c>
     </row>
@@ -12538,7 +12540,7 @@
       <c r="B691" s="4" t="s">
         <v>1376</v>
       </c>
-      <c r="C691" s="7">
+      <c r="C691" s="8">
         <v>232728.40800000002</v>
       </c>
     </row>
@@ -12549,7 +12551,7 @@
       <c r="B692" s="4" t="s">
         <v>1378</v>
       </c>
-      <c r="C692" s="7">
+      <c r="C692" s="8">
         <v>238603.45300000004</v>
       </c>
     </row>
@@ -12560,7 +12562,7 @@
       <c r="B693" s="4" t="s">
         <v>1380</v>
       </c>
-      <c r="C693" s="7">
+      <c r="C693" s="8">
         <v>232728.40800000002</v>
       </c>
     </row>
@@ -12571,7 +12573,7 @@
       <c r="B694" s="4" t="s">
         <v>1382</v>
       </c>
-      <c r="C694" s="7">
+      <c r="C694" s="8">
         <v>338159.66800000001</v>
       </c>
     </row>
@@ -12582,18 +12584,18 @@
       <c r="B695" s="4" t="s">
         <v>1384</v>
       </c>
-      <c r="C695" s="7">
+      <c r="C695" s="8">
         <v>329332.76199999999</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A696" s="6" t="s">
+      <c r="A696" s="5" t="s">
         <v>1385</v>
       </c>
-      <c r="B696" s="6" t="s">
+      <c r="B696" s="5" t="s">
         <v>1386</v>
       </c>
-      <c r="C696" s="7"/>
+      <c r="C696" s="8"/>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A697" s="4" t="s">
@@ -12602,7 +12604,7 @@
       <c r="B697" s="4" t="s">
         <v>1388</v>
       </c>
-      <c r="C697" s="7">
+      <c r="C697" s="8">
         <v>449802.08900000004</v>
       </c>
     </row>
@@ -12613,18 +12615,18 @@
       <c r="B698" s="4" t="s">
         <v>1390</v>
       </c>
-      <c r="C698" s="7">
+      <c r="C698" s="8">
         <v>449802.08900000004</v>
       </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A699" s="6" t="s">
+      <c r="A699" s="5" t="s">
         <v>1391</v>
       </c>
-      <c r="B699" s="6" t="s">
+      <c r="B699" s="5" t="s">
         <v>1392</v>
       </c>
-      <c r="C699" s="7"/>
+      <c r="C699" s="8"/>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A700" s="4" t="s">
@@ -12633,7 +12635,7 @@
       <c r="B700" s="4" t="s">
         <v>1394</v>
       </c>
-      <c r="C700" s="7">
+      <c r="C700" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12644,18 +12646,18 @@
       <c r="B701" s="4" t="s">
         <v>1396</v>
       </c>
-      <c r="C701" s="7">
+      <c r="C701" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A702" s="6" t="s">
+      <c r="A702" s="5" t="s">
         <v>1397</v>
       </c>
-      <c r="B702" s="6" t="s">
+      <c r="B702" s="5" t="s">
         <v>1398</v>
       </c>
-      <c r="C702" s="7"/>
+      <c r="C702" s="8"/>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A703" s="4" t="s">
@@ -12664,7 +12666,7 @@
       <c r="B703" s="4" t="s">
         <v>1400</v>
       </c>
-      <c r="C703" s="7">
+      <c r="C703" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12675,18 +12677,18 @@
       <c r="B704" s="4" t="s">
         <v>1402</v>
       </c>
-      <c r="C704" s="7">
+      <c r="C704" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A705" s="6" t="s">
+      <c r="A705" s="5" t="s">
         <v>1403</v>
       </c>
-      <c r="B705" s="6" t="s">
+      <c r="B705" s="5" t="s">
         <v>1404</v>
       </c>
-      <c r="C705" s="7"/>
+      <c r="C705" s="8"/>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A706" s="4" t="s">
@@ -12695,18 +12697,18 @@
       <c r="B706" s="4" t="s">
         <v>1406</v>
       </c>
-      <c r="C706" s="7">
+      <c r="C706" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A707" s="6" t="s">
+      <c r="A707" s="5" t="s">
         <v>1407</v>
       </c>
-      <c r="B707" s="6" t="s">
+      <c r="B707" s="5" t="s">
         <v>1408</v>
       </c>
-      <c r="C707" s="7"/>
+      <c r="C707" s="8"/>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A708" s="4" t="s">
@@ -12715,7 +12717,7 @@
       <c r="B708" s="4" t="s">
         <v>1410</v>
       </c>
-      <c r="C708" s="7">
+      <c r="C708" s="8">
         <v>602566.32700000005</v>
       </c>
     </row>
@@ -12726,7 +12728,7 @@
       <c r="B709" s="4" t="s">
         <v>1412</v>
       </c>
-      <c r="C709" s="7">
+      <c r="C709" s="8">
         <v>577991.60100000014</v>
       </c>
     </row>
@@ -12737,7 +12739,7 @@
       <c r="B710" s="4" t="s">
         <v>1414</v>
       </c>
-      <c r="C710" s="7">
+      <c r="C710" s="8">
         <v>1573985.4020000002</v>
       </c>
     </row>
@@ -12748,7 +12750,7 @@
       <c r="B711" s="4" t="s">
         <v>1416</v>
       </c>
-      <c r="C711" s="7">
+      <c r="C711" s="8">
         <v>1523224.34</v>
       </c>
     </row>
@@ -12759,7 +12761,7 @@
       <c r="B712" s="4" t="s">
         <v>1418</v>
       </c>
-      <c r="C712" s="7">
+      <c r="C712" s="8">
         <v>2875997.3000000003</v>
       </c>
     </row>
@@ -12770,18 +12772,18 @@
       <c r="B713" s="4" t="s">
         <v>1420</v>
       </c>
-      <c r="C713" s="7">
+      <c r="C713" s="8">
         <v>742767.94900000002</v>
       </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A714" s="6" t="s">
+      <c r="A714" s="5" t="s">
         <v>1421</v>
       </c>
-      <c r="B714" s="6" t="s">
+      <c r="B714" s="5" t="s">
         <v>1422</v>
       </c>
-      <c r="C714" s="7"/>
+      <c r="C714" s="8"/>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A715" s="4" t="s">
@@ -12790,7 +12792,7 @@
       <c r="B715" s="4" t="s">
         <v>1424</v>
       </c>
-      <c r="C715" s="7">
+      <c r="C715" s="8">
         <v>813319.60600000003</v>
       </c>
     </row>
@@ -12801,7 +12803,7 @@
       <c r="B716" s="4" t="s">
         <v>1426</v>
       </c>
-      <c r="C716" s="7">
+      <c r="C716" s="8">
         <v>139879.03599999999</v>
       </c>
     </row>
@@ -12812,7 +12814,7 @@
       <c r="B717" s="4" t="s">
         <v>1428</v>
       </c>
-      <c r="C717" s="7">
+      <c r="C717" s="8">
         <v>242688.6</v>
       </c>
     </row>
@@ -12823,7 +12825,7 @@
       <c r="B718" s="4" t="s">
         <v>1430</v>
       </c>
-      <c r="C718" s="7">
+      <c r="C718" s="8">
         <v>114760.8</v>
       </c>
     </row>
@@ -12834,7 +12836,7 @@
       <c r="B719" s="4" t="s">
         <v>1432</v>
       </c>
-      <c r="C719" s="7">
+      <c r="C719" s="8">
         <v>110880.00000000001</v>
       </c>
     </row>
@@ -12845,7 +12847,7 @@
       <c r="B720" s="4" t="s">
         <v>1434</v>
       </c>
-      <c r="C720" s="7">
+      <c r="C720" s="8">
         <v>172874.98800000001</v>
       </c>
     </row>
@@ -12856,7 +12858,7 @@
       <c r="B721" s="4" t="s">
         <v>1436</v>
       </c>
-      <c r="C721" s="7">
+      <c r="C721" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12867,7 +12869,7 @@
       <c r="B722" s="4" t="s">
         <v>1438</v>
       </c>
-      <c r="C722" s="7">
+      <c r="C722" s="8">
         <v>81499.429000000004</v>
       </c>
     </row>
@@ -12878,7 +12880,7 @@
       <c r="B723" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="C723" s="7">
+      <c r="C723" s="8">
         <v>60936.865000000005</v>
       </c>
     </row>
@@ -12889,7 +12891,7 @@
       <c r="B724" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="C724" s="7">
+      <c r="C724" s="8">
         <v>101561.592</v>
       </c>
     </row>
@@ -12900,7 +12902,7 @@
       <c r="B725" s="4" t="s">
         <v>1444</v>
       </c>
-      <c r="C725" s="7">
+      <c r="C725" s="8">
         <v>433359.33300000004</v>
       </c>
     </row>
@@ -12911,7 +12913,7 @@
       <c r="B726" s="4" t="s">
         <v>1446</v>
       </c>
-      <c r="C726" s="7">
+      <c r="C726" s="8">
         <v>345743.05700000003</v>
       </c>
     </row>
@@ -12922,7 +12924,7 @@
       <c r="B727" s="4" t="s">
         <v>1448</v>
       </c>
-      <c r="C727" s="7">
+      <c r="C727" s="8">
         <v>79677.301000000007</v>
       </c>
     </row>
@@ -12933,7 +12935,7 @@
       <c r="B728" s="4" t="s">
         <v>1450</v>
       </c>
-      <c r="C728" s="7">
+      <c r="C728" s="8">
         <v>241904.91600000003</v>
       </c>
     </row>
@@ -12944,7 +12946,7 @@
       <c r="B729" s="4" t="s">
         <v>1452</v>
       </c>
-      <c r="C729" s="7">
+      <c r="C729" s="8">
         <v>241904.91600000003</v>
       </c>
     </row>
@@ -12955,7 +12957,7 @@
       <c r="B730" s="4" t="s">
         <v>1454</v>
       </c>
-      <c r="C730" s="7">
+      <c r="C730" s="8">
         <v>125207.21400000002</v>
       </c>
     </row>
@@ -12966,7 +12968,7 @@
       <c r="B731" s="4" t="s">
         <v>1456</v>
       </c>
-      <c r="C731" s="7">
+      <c r="C731" s="8">
         <v>299200</v>
       </c>
     </row>
@@ -12977,7 +12979,7 @@
       <c r="B732" s="4" t="s">
         <v>1458</v>
       </c>
-      <c r="C732" s="7">
+      <c r="C732" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12988,7 +12990,7 @@
       <c r="B733" s="4" t="s">
         <v>1460</v>
       </c>
-      <c r="C733" s="7">
+      <c r="C733" s="8">
         <v>30461.222000000002</v>
       </c>
     </row>
@@ -12999,7 +13001,7 @@
       <c r="B734" s="4" t="s">
         <v>1462</v>
       </c>
-      <c r="C734" s="7">
+      <c r="C734" s="8">
         <v>159785.40600000002</v>
       </c>
     </row>
@@ -13010,7 +13012,7 @@
       <c r="B735" s="4" t="s">
         <v>1464</v>
       </c>
-      <c r="C735" s="7">
+      <c r="C735" s="8">
         <v>126054.65400000001</v>
       </c>
     </row>
@@ -13021,7 +13023,7 @@
       <c r="B736" s="4" t="s">
         <v>1466</v>
       </c>
-      <c r="C736" s="7">
+      <c r="C736" s="8">
         <v>48744.47600000001</v>
       </c>
     </row>
@@ -13032,7 +13034,7 @@
       <c r="B737" s="4" t="s">
         <v>1468</v>
       </c>
-      <c r="C737" s="7">
+      <c r="C737" s="8">
         <v>70447.553000000014</v>
       </c>
     </row>
@@ -13043,7 +13045,7 @@
       <c r="B738" s="4" t="s">
         <v>1470</v>
       </c>
-      <c r="C738" s="7">
+      <c r="C738" s="8">
         <v>126948.04100000001</v>
       </c>
     </row>
@@ -13054,7 +13056,7 @@
       <c r="B739" s="4" t="s">
         <v>1472</v>
       </c>
-      <c r="C739" s="7">
+      <c r="C739" s="8">
         <v>120911.62600000002</v>
       </c>
     </row>
@@ -13065,7 +13067,7 @@
       <c r="B740" s="4" t="s">
         <v>1474</v>
       </c>
-      <c r="C740" s="7">
+      <c r="C740" s="8">
         <v>172631.11800000002</v>
       </c>
     </row>
@@ -13076,7 +13078,7 @@
       <c r="B741" s="4" t="s">
         <v>1476</v>
       </c>
-      <c r="C741" s="7">
+      <c r="C741" s="8">
         <v>211591.77600000001</v>
       </c>
     </row>
@@ -13087,7 +13089,7 @@
       <c r="B742" s="4" t="s">
         <v>1478</v>
       </c>
-      <c r="C742" s="7">
+      <c r="C742" s="8">
         <v>140435.48200000002</v>
       </c>
     </row>
@@ -13098,7 +13100,7 @@
       <c r="B743" s="4" t="s">
         <v>1480</v>
       </c>
-      <c r="C743" s="7">
+      <c r="C743" s="8">
         <v>109019.95500000002</v>
       </c>
     </row>
@@ -13109,7 +13111,7 @@
       <c r="B744" s="4" t="s">
         <v>1482</v>
       </c>
-      <c r="C744" s="7">
+      <c r="C744" s="8">
         <v>71075.96100000001</v>
       </c>
     </row>
@@ -13120,7 +13122,7 @@
       <c r="B745" s="4" t="s">
         <v>1484</v>
       </c>
-      <c r="C745" s="7">
+      <c r="C745" s="8">
         <v>167759.47099999999</v>
       </c>
     </row>
@@ -13131,7 +13133,7 @@
       <c r="B746" s="4" t="s">
         <v>1486</v>
       </c>
-      <c r="C746" s="7">
+      <c r="C746" s="8">
         <v>60929.781000000003</v>
       </c>
     </row>
@@ -13142,7 +13144,7 @@
       <c r="B747" s="4" t="s">
         <v>1488</v>
       </c>
-      <c r="C747" s="7">
+      <c r="C747" s="8">
         <v>353214.14700000006</v>
       </c>
     </row>
@@ -13153,7 +13155,7 @@
       <c r="B748" s="4" t="s">
         <v>1490</v>
       </c>
-      <c r="C748" s="7">
+      <c r="C748" s="8">
         <v>139609.41500000001</v>
       </c>
     </row>
@@ -13164,7 +13166,7 @@
       <c r="B749" s="4" t="s">
         <v>1492</v>
       </c>
-      <c r="C749" s="7">
+      <c r="C749" s="8">
         <v>34989.867000000006</v>
       </c>
     </row>
@@ -13175,7 +13177,7 @@
       <c r="B750" s="4" t="s">
         <v>1494</v>
       </c>
-      <c r="C750" s="7">
+      <c r="C750" s="8">
         <v>76255.850000000006</v>
       </c>
     </row>
@@ -13186,7 +13188,7 @@
       <c r="B751" s="4" t="s">
         <v>1496</v>
       </c>
-      <c r="C751" s="7">
+      <c r="C751" s="8">
         <v>179092.45200000002</v>
       </c>
     </row>
@@ -13197,7 +13199,7 @@
       <c r="B752" s="4" t="s">
         <v>1498</v>
       </c>
-      <c r="C752" s="7">
+      <c r="C752" s="8">
         <v>122134.58400000002</v>
       </c>
     </row>
@@ -13208,7 +13210,7 @@
       <c r="B753" s="4" t="s">
         <v>1500</v>
       </c>
-      <c r="C753" s="7">
+      <c r="C753" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13219,7 +13221,7 @@
       <c r="B754" s="4" t="s">
         <v>1502</v>
       </c>
-      <c r="C754" s="7">
+      <c r="C754" s="8">
         <v>217421.864</v>
       </c>
     </row>
@@ -13230,7 +13232,7 @@
       <c r="B755" s="4" t="s">
         <v>1504</v>
       </c>
-      <c r="C755" s="7">
+      <c r="C755" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13241,7 +13243,7 @@
       <c r="B756" s="4" t="s">
         <v>1506</v>
       </c>
-      <c r="C756" s="7">
+      <c r="C756" s="8">
         <v>217421.864</v>
       </c>
     </row>
@@ -13252,7 +13254,7 @@
       <c r="B757" s="4" t="s">
         <v>1508</v>
       </c>
-      <c r="C757" s="7">
+      <c r="C757" s="8">
         <v>217421.864</v>
       </c>
     </row>
@@ -13263,7 +13265,7 @@
       <c r="B758" s="4" t="s">
         <v>1510</v>
       </c>
-      <c r="C758" s="7">
+      <c r="C758" s="8">
         <v>217421.864</v>
       </c>
     </row>
@@ -13274,7 +13276,7 @@
       <c r="B759" s="4" t="s">
         <v>1512</v>
       </c>
-      <c r="C759" s="7">
+      <c r="C759" s="8">
         <v>87942.8</v>
       </c>
     </row>
@@ -13285,7 +13287,7 @@
       <c r="B760" s="4" t="s">
         <v>1514</v>
       </c>
-      <c r="C760" s="7">
+      <c r="C760" s="8">
         <v>296208</v>
       </c>
     </row>
@@ -13296,7 +13298,7 @@
       <c r="B761" s="4" t="s">
         <v>1516</v>
       </c>
-      <c r="C761" s="7">
+      <c r="C761" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13307,7 +13309,7 @@
       <c r="B762" s="4" t="s">
         <v>1518</v>
       </c>
-      <c r="C762" s="7">
+      <c r="C762" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13318,7 +13320,7 @@
       <c r="B763" s="4" t="s">
         <v>1520</v>
       </c>
-      <c r="C763" s="7">
+      <c r="C763" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13329,7 +13331,7 @@
       <c r="B764" s="4" t="s">
         <v>1522</v>
       </c>
-      <c r="C764" s="7">
+      <c r="C764" s="8">
         <v>165737.649</v>
       </c>
     </row>
@@ -13340,7 +13342,7 @@
       <c r="B765" s="4" t="s">
         <v>1524</v>
       </c>
-      <c r="C765" s="7">
+      <c r="C765" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13351,7 +13353,7 @@
       <c r="B766" s="4" t="s">
         <v>1526</v>
       </c>
-      <c r="C766" s="7">
+      <c r="C766" s="8">
         <v>97579.933000000005</v>
       </c>
     </row>
@@ -13362,7 +13364,7 @@
       <c r="B767" s="4" t="s">
         <v>1528</v>
       </c>
-      <c r="C767" s="7">
+      <c r="C767" s="8">
         <v>44356.146999999997</v>
       </c>
     </row>
@@ -13373,7 +13375,7 @@
       <c r="B768" s="4" t="s">
         <v>1530</v>
       </c>
-      <c r="C768" s="7">
+      <c r="C768" s="8">
         <v>167759.47099999999</v>
       </c>
     </row>
@@ -13384,7 +13386,7 @@
       <c r="B769" s="4" t="s">
         <v>1532</v>
       </c>
-      <c r="C769" s="7">
+      <c r="C769" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13395,7 +13397,7 @@
       <c r="B770" s="4" t="s">
         <v>1534</v>
       </c>
-      <c r="C770" s="7">
+      <c r="C770" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13406,7 +13408,7 @@
       <c r="B771" s="4" t="s">
         <v>1536</v>
       </c>
-      <c r="C771" s="7">
+      <c r="C771" s="8">
         <v>283381.30700000003</v>
       </c>
     </row>
@@ -13417,7 +13419,7 @@
       <c r="B772" s="4" t="s">
         <v>1538</v>
       </c>
-      <c r="C772" s="7">
+      <c r="C772" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13428,16 +13430,17 @@
       <c r="B773" s="4" t="s">
         <v>1540</v>
       </c>
-      <c r="C773" s="7"/>
+      <c r="C773" s="8"/>
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
         <v>1541</v>
       </c>
       <c r="B774" s="2"/>
-      <c r="C774" s="7"/>
+      <c r="C774" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>